--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9CC27F5-2752-491D-9B16-6FC11E4BC63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF6A974-5FCD-4CB5-A970-5C88A7426C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -635,8 +635,8 @@
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
@@ -676,7 +676,7 @@
     <xf numFmtId="0" fontId="10" fillId="16" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -688,43 +688,43 @@
     <xf numFmtId="0" fontId="11" fillId="18" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -763,22 +763,22 @@
     <xf numFmtId="49" fontId="10" fillId="22" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="23" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -844,7 +844,7 @@
     <xf numFmtId="49" fontId="7" fillId="25" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="23" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -883,7 +883,7 @@
     <xf numFmtId="49" fontId="9" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -904,10 +904,10 @@
     <xf numFmtId="0" fontId="12" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
@@ -1341,8 +1341,8 @@
       <c r="E10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>18</v>
+      <c r="F10" s="15" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="3:6" x14ac:dyDescent="0.25">
@@ -3461,11 +3461,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3482,6 +3477,11 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF6A974-5FCD-4CB5-A970-5C88A7426C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BED9184-5653-42D7-94BE-3AE6A246C623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
+    <workbookView xWindow="1245" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="29">
   <si>
     <t>Código</t>
   </si>
@@ -119,6 +119,9 @@
   <si>
     <t>Carnaval</t>
   </si>
+  <si>
+    <t>Feito</t>
+  </si>
 </sst>
 </file>
 
@@ -127,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +239,14 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="26">
@@ -640,7 +651,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -862,27 +873,6 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="8" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="8" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -895,6 +885,15 @@
     <xf numFmtId="0" fontId="13" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="17" fontId="8" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -910,6 +909,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Euro" xfId="2" xr:uid="{DD3A81DB-1FA7-4E0F-9A23-1484AF7F90C2}"/>
@@ -1355,8 +1367,8 @@
       <c r="E11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>18</v>
+      <c r="F11" s="101" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="3:6" x14ac:dyDescent="0.25">
@@ -1493,17 +1505,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>45931</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="99" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="79"/>
       <c r="D20" s="79"/>
       <c r="E20" s="27"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="96" t="s">
+      <c r="G20" s="92" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="29"/>
@@ -1562,13 +1574,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
-      <c r="B21" s="89"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="52"/>
       <c r="D21" s="52"/>
       <c r="E21" s="23"/>
       <c r="F21" s="18"/>
-      <c r="G21" s="97"/>
+      <c r="G21" s="93"/>
       <c r="H21" s="30"/>
       <c r="I21" s="52"/>
       <c r="J21" s="58">
@@ -1625,13 +1637,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="98"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="23"/>
       <c r="F22" s="18"/>
-      <c r="G22" s="97"/>
+      <c r="G22" s="93"/>
       <c r="H22" s="30"/>
       <c r="I22" s="52"/>
       <c r="J22" s="58">
@@ -1688,13 +1700,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
-      <c r="B23" s="89"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="52"/>
       <c r="D23" s="52"/>
       <c r="E23" s="23"/>
       <c r="F23" s="18"/>
-      <c r="G23" s="97"/>
+      <c r="G23" s="93"/>
       <c r="H23" s="30"/>
       <c r="I23" s="52"/>
       <c r="J23" s="53"/>
@@ -1749,15 +1761,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
-      <c r="B24" s="90" t="s">
+      <c r="A24" s="90"/>
+      <c r="B24" s="97" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="52"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
       <c r="F24" s="19"/>
-      <c r="G24" s="97"/>
+      <c r="G24" s="93"/>
       <c r="H24" s="33"/>
       <c r="I24" s="52"/>
       <c r="J24" s="58">
@@ -1812,13 +1824,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="52"/>
       <c r="D25" s="52"/>
       <c r="E25" s="52"/>
       <c r="F25" s="20"/>
-      <c r="G25" s="97"/>
+      <c r="G25" s="93"/>
       <c r="H25" s="33"/>
       <c r="I25" s="52"/>
       <c r="J25" s="58">
@@ -1873,13 +1885,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="91"/>
+      <c r="A26" s="91"/>
+      <c r="B26" s="100"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="E26" s="56"/>
       <c r="F26" s="22"/>
-      <c r="G26" s="98"/>
+      <c r="G26" s="94"/>
       <c r="H26" s="35"/>
       <c r="I26" s="56"/>
       <c r="J26" s="59">
@@ -1934,10 +1946,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="85">
+      <c r="A27" s="89">
         <v>45962</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="99" t="s">
         <v>19</v>
       </c>
       <c r="C27" s="21"/>
@@ -2005,8 +2017,8 @@
       <c r="AG27" s="28"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
-      <c r="B28" s="89"/>
+      <c r="A28" s="90"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="50" t="s">
@@ -2072,8 +2084,8 @@
       <c r="AG28" s="26"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
-      <c r="B29" s="89"/>
+      <c r="A29" s="90"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="50" t="s">
@@ -2139,8 +2151,8 @@
       <c r="AG29" s="26"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
-      <c r="B30" s="89"/>
+      <c r="A30" s="90"/>
+      <c r="B30" s="98"/>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="50" t="s">
@@ -2206,8 +2218,8 @@
       <c r="AG30" s="26"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="86"/>
-      <c r="B31" s="90" t="s">
+      <c r="A31" s="90"/>
+      <c r="B31" s="97" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="19"/>
@@ -2259,8 +2271,8 @@
       <c r="AG31" s="26"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="86"/>
-      <c r="B32" s="89"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="98"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
       <c r="E32" s="52"/>
@@ -2310,8 +2322,8 @@
       <c r="AG32" s="26"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="91"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="100"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
       <c r="E33" s="56"/>
@@ -2361,13 +2373,13 @@
       <c r="AG33" s="36"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="86">
+      <c r="A34" s="90">
         <v>45992</v>
       </c>
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="85" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="70" t="s">
@@ -2382,7 +2394,7 @@
       </c>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
-      <c r="J34" s="92" t="s">
+      <c r="J34" s="85" t="s">
         <v>20</v>
       </c>
       <c r="K34" s="70" t="s">
@@ -2407,7 +2419,7 @@
       <c r="X34" s="37"/>
       <c r="Y34" s="37"/>
       <c r="Z34" s="37"/>
-      <c r="AA34" s="92" t="s">
+      <c r="AA34" s="85" t="s">
         <v>25</v>
       </c>
       <c r="AB34" s="37"/>
@@ -2418,9 +2430,9 @@
       <c r="AG34" s="37"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="86"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="92"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="85"/>
       <c r="D35" s="48" t="s">
         <v>23</v>
       </c>
@@ -2433,7 +2445,7 @@
       </c>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
-      <c r="J35" s="92"/>
+      <c r="J35" s="85"/>
       <c r="K35" s="48" t="s">
         <v>23</v>
       </c>
@@ -2456,7 +2468,7 @@
       <c r="X35" s="37"/>
       <c r="Y35" s="37"/>
       <c r="Z35" s="37"/>
-      <c r="AA35" s="92"/>
+      <c r="AA35" s="85"/>
       <c r="AB35" s="37"/>
       <c r="AC35" s="18"/>
       <c r="AD35" s="18"/>
@@ -2465,9 +2477,9 @@
       <c r="AG35" s="37"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="86"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="92"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="85"/>
       <c r="D36" s="48" t="s">
         <v>23</v>
       </c>
@@ -2480,7 +2492,7 @@
       </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
-      <c r="J36" s="92"/>
+      <c r="J36" s="85"/>
       <c r="K36" s="48" t="s">
         <v>23</v>
       </c>
@@ -2503,7 +2515,7 @@
       <c r="X36" s="37"/>
       <c r="Y36" s="37"/>
       <c r="Z36" s="37"/>
-      <c r="AA36" s="92"/>
+      <c r="AA36" s="85"/>
       <c r="AB36" s="37"/>
       <c r="AC36" s="18"/>
       <c r="AD36" s="18"/>
@@ -2512,9 +2524,9 @@
       <c r="AG36" s="37"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="92"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="85"/>
       <c r="D37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2527,7 +2539,7 @@
       </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
-      <c r="J37" s="92"/>
+      <c r="J37" s="85"/>
       <c r="K37" s="49" t="s">
         <v>24</v>
       </c>
@@ -2550,7 +2562,7 @@
       <c r="X37" s="37"/>
       <c r="Y37" s="37"/>
       <c r="Z37" s="37"/>
-      <c r="AA37" s="92"/>
+      <c r="AA37" s="85"/>
       <c r="AB37" s="37"/>
       <c r="AC37" s="18"/>
       <c r="AD37" s="18"/>
@@ -2559,11 +2571,11 @@
       <c r="AG37" s="37"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="86"/>
-      <c r="B38" s="90" t="s">
+      <c r="A38" s="90"/>
+      <c r="B38" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="92"/>
+      <c r="C38" s="85"/>
       <c r="D38" s="54"/>
       <c r="E38" s="61">
         <v>10793</v>
@@ -2574,7 +2586,7 @@
       </c>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
-      <c r="J38" s="92"/>
+      <c r="J38" s="85"/>
       <c r="K38" s="54"/>
       <c r="L38" s="64">
         <v>10794</v>
@@ -2595,7 +2607,7 @@
       <c r="X38" s="33"/>
       <c r="Y38" s="33"/>
       <c r="Z38" s="33"/>
-      <c r="AA38" s="92"/>
+      <c r="AA38" s="85"/>
       <c r="AB38" s="33"/>
       <c r="AC38" s="19"/>
       <c r="AD38" s="19"/>
@@ -2604,9 +2616,9 @@
       <c r="AG38" s="33"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="92"/>
+      <c r="A39" s="90"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="85"/>
       <c r="D39" s="54"/>
       <c r="E39" s="61">
         <v>10793</v>
@@ -2617,7 +2629,7 @@
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
-      <c r="J39" s="92"/>
+      <c r="J39" s="85"/>
       <c r="K39" s="54"/>
       <c r="L39" s="64">
         <v>10794</v>
@@ -2638,7 +2650,7 @@
       <c r="X39" s="33"/>
       <c r="Y39" s="33"/>
       <c r="Z39" s="33"/>
-      <c r="AA39" s="92"/>
+      <c r="AA39" s="85"/>
       <c r="AB39" s="33"/>
       <c r="AC39" s="20"/>
       <c r="AD39" s="20"/>
@@ -2647,9 +2659,9 @@
       <c r="AG39" s="33"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="86"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="92"/>
+      <c r="A40" s="90"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="85"/>
       <c r="D40" s="57"/>
       <c r="E40" s="61">
         <v>10793</v>
@@ -2660,7 +2672,7 @@
       </c>
       <c r="H40" s="34"/>
       <c r="I40" s="34"/>
-      <c r="J40" s="92"/>
+      <c r="J40" s="85"/>
       <c r="K40" s="55"/>
       <c r="L40" s="67">
         <v>10794</v>
@@ -2681,7 +2693,7 @@
       <c r="X40" s="55"/>
       <c r="Y40" s="55"/>
       <c r="Z40" s="55"/>
-      <c r="AA40" s="92"/>
+      <c r="AA40" s="85"/>
       <c r="AB40" s="55"/>
       <c r="AC40" s="34"/>
       <c r="AD40" s="34"/>
@@ -2690,13 +2702,13 @@
       <c r="AG40" s="55"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="85">
+      <c r="A41" s="89">
         <v>46023</v>
       </c>
-      <c r="B41" s="88" t="s">
+      <c r="B41" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="99" t="s">
+      <c r="C41" s="95" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="38"/>
@@ -2755,9 +2767,9 @@
       <c r="AG41" s="21"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="92"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="98"/>
+      <c r="C42" s="85"/>
       <c r="D42" s="37"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
@@ -2814,9 +2826,9 @@
       <c r="AG42" s="18"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
-      <c r="B43" s="89"/>
-      <c r="C43" s="92"/>
+      <c r="A43" s="90"/>
+      <c r="B43" s="98"/>
+      <c r="C43" s="85"/>
       <c r="D43" s="37"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
@@ -2873,9 +2885,9 @@
       <c r="AG43" s="18"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="92"/>
+      <c r="A44" s="90"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="85"/>
       <c r="D44" s="37"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
@@ -2932,11 +2944,11 @@
       <c r="AG44" s="18"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="86"/>
-      <c r="B45" s="90" t="s">
+      <c r="A45" s="90"/>
+      <c r="B45" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="85"/>
       <c r="D45" s="33"/>
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
@@ -2985,9 +2997,9 @@
       <c r="AG45" s="19"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="86"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="92"/>
+      <c r="A46" s="90"/>
+      <c r="B46" s="98"/>
+      <c r="C46" s="85"/>
       <c r="D46" s="33"/>
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
@@ -3034,9 +3046,9 @@
       <c r="AG46" s="20"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="87"/>
-      <c r="B47" s="91"/>
-      <c r="C47" s="100"/>
+      <c r="A47" s="91"/>
+      <c r="B47" s="100"/>
+      <c r="C47" s="96"/>
       <c r="D47" s="35"/>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
@@ -3083,10 +3095,10 @@
       <c r="AG47" s="22"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="85">
+      <c r="A48" s="89">
         <v>46054</v>
       </c>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="99" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="40"/>
@@ -3115,7 +3127,7 @@
       <c r="P48" s="40"/>
       <c r="Q48" s="40"/>
       <c r="R48" s="38"/>
-      <c r="S48" s="93" t="s">
+      <c r="S48" s="86" t="s">
         <v>27</v>
       </c>
       <c r="T48" s="83">
@@ -3142,8 +3154,8 @@
       <c r="AG48" s="44"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="86"/>
-      <c r="B49" s="89"/>
+      <c r="A49" s="90"/>
+      <c r="B49" s="98"/>
       <c r="C49" s="41"/>
       <c r="D49" s="37"/>
       <c r="E49" s="69" t="s">
@@ -3170,7 +3182,7 @@
       <c r="P49" s="41"/>
       <c r="Q49" s="41"/>
       <c r="R49" s="37"/>
-      <c r="S49" s="94"/>
+      <c r="S49" s="87"/>
       <c r="T49" s="68">
         <v>5425</v>
       </c>
@@ -3195,8 +3207,8 @@
       <c r="AG49" s="45"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="86"/>
-      <c r="B50" s="89"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="98"/>
       <c r="C50" s="41"/>
       <c r="D50" s="37"/>
       <c r="E50" s="69" t="s">
@@ -3223,7 +3235,7 @@
       <c r="P50" s="41"/>
       <c r="Q50" s="41"/>
       <c r="R50" s="37"/>
-      <c r="S50" s="94"/>
+      <c r="S50" s="87"/>
       <c r="T50" s="68">
         <v>5425</v>
       </c>
@@ -3248,8 +3260,8 @@
       <c r="AG50" s="45"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="86"/>
-      <c r="B51" s="89"/>
+      <c r="A51" s="90"/>
+      <c r="B51" s="98"/>
       <c r="C51" s="41"/>
       <c r="D51" s="37"/>
       <c r="E51" s="69" t="s">
@@ -3276,7 +3288,7 @@
       <c r="P51" s="41"/>
       <c r="Q51" s="41"/>
       <c r="R51" s="37"/>
-      <c r="S51" s="94"/>
+      <c r="S51" s="87"/>
       <c r="T51" s="68">
         <v>5425</v>
       </c>
@@ -3301,8 +3313,8 @@
       <c r="AG51" s="45"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="86"/>
-      <c r="B52" s="90" t="s">
+      <c r="A52" s="90"/>
+      <c r="B52" s="97" t="s">
         <v>22</v>
       </c>
       <c r="C52" s="42"/>
@@ -3331,7 +3343,7 @@
       <c r="P52" s="42"/>
       <c r="Q52" s="42"/>
       <c r="R52" s="33"/>
-      <c r="S52" s="94"/>
+      <c r="S52" s="87"/>
       <c r="T52" s="68">
         <v>5425</v>
       </c>
@@ -3356,8 +3368,8 @@
       <c r="AG52" s="46"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="86"/>
-      <c r="B53" s="89"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="98"/>
       <c r="C53" s="42"/>
       <c r="D53" s="33"/>
       <c r="E53" s="64">
@@ -3384,7 +3396,7 @@
       <c r="P53" s="42"/>
       <c r="Q53" s="42"/>
       <c r="R53" s="33"/>
-      <c r="S53" s="94"/>
+      <c r="S53" s="87"/>
       <c r="T53" s="68">
         <v>5425</v>
       </c>
@@ -3409,8 +3421,8 @@
       <c r="AG53" s="46"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="87"/>
-      <c r="B54" s="91"/>
+      <c r="A54" s="91"/>
+      <c r="B54" s="100"/>
       <c r="C54" s="43"/>
       <c r="D54" s="35"/>
       <c r="E54" s="65">
@@ -3437,7 +3449,7 @@
       <c r="P54" s="43"/>
       <c r="Q54" s="43"/>
       <c r="R54" s="35"/>
-      <c r="S54" s="95"/>
+      <c r="S54" s="88"/>
       <c r="T54" s="35"/>
       <c r="U54" s="84">
         <v>5425</v>
@@ -3461,6 +3473,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3477,11 +3494,6 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4C43C2-FD76-42AD-B7FB-24F687DA2BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489BB710-5B00-4738-9611-75A213742E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +233,12 @@
       <b/>
       <sz val="11"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -640,7 +646,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -862,27 +868,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -895,6 +880,15 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -909,6 +903,33 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="16" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1493,17 +1514,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="85">
+      <c r="A20" s="89">
         <v>45931</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="99" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
       <c r="E20" s="26"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="96" t="s">
+      <c r="G20" s="92" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="28"/>
@@ -1562,13 +1583,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
-      <c r="B21" s="89"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="22"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="97"/>
+      <c r="G21" s="93"/>
       <c r="H21" s="29"/>
       <c r="I21" s="51"/>
       <c r="J21" s="57">
@@ -1625,13 +1646,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="86"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="98"/>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="22"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="97"/>
+      <c r="G22" s="93"/>
       <c r="H22" s="29"/>
       <c r="I22" s="51"/>
       <c r="J22" s="57">
@@ -1688,13 +1709,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
-      <c r="B23" s="89"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="22"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="97"/>
+      <c r="G23" s="93"/>
       <c r="H23" s="29"/>
       <c r="I23" s="51"/>
       <c r="J23" s="52"/>
@@ -1749,15 +1770,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="86"/>
-      <c r="B24" s="90" t="s">
+      <c r="A24" s="90"/>
+      <c r="B24" s="97" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="97"/>
+      <c r="G24" s="93"/>
       <c r="H24" s="32"/>
       <c r="I24" s="51"/>
       <c r="J24" s="57">
@@ -1812,13 +1833,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="97"/>
+      <c r="G25" s="93"/>
       <c r="H25" s="32"/>
       <c r="I25" s="51"/>
       <c r="J25" s="57">
@@ -1873,13 +1894,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="91"/>
+      <c r="A26" s="91"/>
+      <c r="B26" s="100"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
       <c r="E26" s="55"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="98"/>
+      <c r="G26" s="94"/>
       <c r="H26" s="34"/>
       <c r="I26" s="55"/>
       <c r="J26" s="58">
@@ -1934,10 +1955,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="85">
+      <c r="A27" s="89">
         <v>45962</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="99" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2005,8 +2026,8 @@
       <c r="AG27" s="27"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="86"/>
-      <c r="B28" s="89"/>
+      <c r="A28" s="90"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="49" t="s">
@@ -2072,8 +2093,8 @@
       <c r="AG28" s="25"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="86"/>
-      <c r="B29" s="89"/>
+      <c r="A29" s="90"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="49" t="s">
@@ -2139,8 +2160,8 @@
       <c r="AG29" s="25"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="86"/>
-      <c r="B30" s="89"/>
+      <c r="A30" s="90"/>
+      <c r="B30" s="98"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="49" t="s">
@@ -2206,8 +2227,8 @@
       <c r="AG30" s="25"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="86"/>
-      <c r="B31" s="90" t="s">
+      <c r="A31" s="90"/>
+      <c r="B31" s="97" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="18"/>
@@ -2259,8 +2280,8 @@
       <c r="AG31" s="25"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="86"/>
-      <c r="B32" s="89"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="98"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="51"/>
@@ -2310,8 +2331,8 @@
       <c r="AG32" s="25"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="91"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="100"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
       <c r="E33" s="55"/>
@@ -2361,13 +2382,13 @@
       <c r="AG33" s="35"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="86">
+      <c r="A34" s="90">
         <v>45992</v>
       </c>
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="85" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="69" t="s">
@@ -2382,7 +2403,7 @@
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="92" t="s">
+      <c r="J34" s="85" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="69" t="s">
@@ -2407,7 +2428,7 @@
       <c r="X34" s="36"/>
       <c r="Y34" s="36"/>
       <c r="Z34" s="36"/>
-      <c r="AA34" s="92" t="s">
+      <c r="AA34" s="85" t="s">
         <v>24</v>
       </c>
       <c r="AB34" s="36"/>
@@ -2418,9 +2439,9 @@
       <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="86"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="92"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="85"/>
       <c r="D35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2433,7 +2454,7 @@
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="92"/>
+      <c r="J35" s="85"/>
       <c r="K35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2456,7 +2477,7 @@
       <c r="X35" s="36"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
-      <c r="AA35" s="92"/>
+      <c r="AA35" s="85"/>
       <c r="AB35" s="36"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
@@ -2465,9 +2486,9 @@
       <c r="AG35" s="36"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="86"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="92"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="98"/>
+      <c r="C36" s="85"/>
       <c r="D36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2480,7 +2501,7 @@
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-      <c r="J36" s="92"/>
+      <c r="J36" s="85"/>
       <c r="K36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2503,7 +2524,7 @@
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="92"/>
+      <c r="AA36" s="85"/>
       <c r="AB36" s="36"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
@@ -2512,9 +2533,9 @@
       <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="92"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="85"/>
       <c r="D37" s="47" t="s">
         <v>22</v>
       </c>
@@ -2527,7 +2548,7 @@
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="92"/>
+      <c r="J37" s="85"/>
       <c r="K37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2550,7 +2571,7 @@
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
-      <c r="AA37" s="92"/>
+      <c r="AA37" s="85"/>
       <c r="AB37" s="36"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
@@ -2559,11 +2580,11 @@
       <c r="AG37" s="36"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="86"/>
-      <c r="B38" s="90" t="s">
+      <c r="A38" s="90"/>
+      <c r="B38" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="92"/>
+      <c r="C38" s="85"/>
       <c r="D38" s="53"/>
       <c r="E38" s="60">
         <v>10793</v>
@@ -2574,7 +2595,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="92"/>
+      <c r="J38" s="85"/>
       <c r="K38" s="53"/>
       <c r="L38" s="63">
         <v>10794</v>
@@ -2595,7 +2616,7 @@
       <c r="X38" s="32"/>
       <c r="Y38" s="32"/>
       <c r="Z38" s="32"/>
-      <c r="AA38" s="92"/>
+      <c r="AA38" s="85"/>
       <c r="AB38" s="32"/>
       <c r="AC38" s="18"/>
       <c r="AD38" s="18"/>
@@ -2604,9 +2625,9 @@
       <c r="AG38" s="32"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="92"/>
+      <c r="A39" s="90"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="85"/>
       <c r="D39" s="53"/>
       <c r="E39" s="60">
         <v>10793</v>
@@ -2617,7 +2638,7 @@
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="92"/>
+      <c r="J39" s="85"/>
       <c r="K39" s="53"/>
       <c r="L39" s="63">
         <v>10794</v>
@@ -2638,7 +2659,7 @@
       <c r="X39" s="32"/>
       <c r="Y39" s="32"/>
       <c r="Z39" s="32"/>
-      <c r="AA39" s="92"/>
+      <c r="AA39" s="85"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="19"/>
       <c r="AD39" s="19"/>
@@ -2647,9 +2668,9 @@
       <c r="AG39" s="32"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="86"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="92"/>
+      <c r="A40" s="90"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="85"/>
       <c r="D40" s="56"/>
       <c r="E40" s="60">
         <v>10793</v>
@@ -2660,7 +2681,7 @@
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
-      <c r="J40" s="92"/>
+      <c r="J40" s="85"/>
       <c r="K40" s="54"/>
       <c r="L40" s="66">
         <v>10794</v>
@@ -2681,7 +2702,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="54"/>
       <c r="Z40" s="54"/>
-      <c r="AA40" s="92"/>
+      <c r="AA40" s="85"/>
       <c r="AB40" s="54"/>
       <c r="AC40" s="33"/>
       <c r="AD40" s="33"/>
@@ -2690,13 +2711,13 @@
       <c r="AG40" s="54"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="85">
+      <c r="A41" s="89">
         <v>46023</v>
       </c>
-      <c r="B41" s="88" t="s">
+      <c r="B41" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="99" t="s">
+      <c r="C41" s="95" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37"/>
@@ -2706,25 +2727,23 @@
       <c r="H41" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="76" t="s">
-        <v>23</v>
-      </c>
+      <c r="I41" s="101"/>
+      <c r="J41" s="101"/>
       <c r="K41" s="37"/>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
+      <c r="O41" s="76" t="s">
+        <v>23</v>
+      </c>
       <c r="P41" s="76" t="s">
         <v>23</v>
       </c>
       <c r="Q41" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="R41" s="77" t="s">
-        <v>25</v>
+      <c r="R41" s="104" t="s">
+        <v>23</v>
       </c>
       <c r="S41" s="20"/>
       <c r="T41" s="20"/>
@@ -2745,19 +2764,19 @@
       <c r="AC41" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AD41" s="77" t="s">
+      <c r="AD41" s="103"/>
+      <c r="AE41" s="65">
+        <v>10794</v>
+      </c>
+      <c r="AF41" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AE41" s="65">
-        <v>10794</v>
-      </c>
-      <c r="AF41" s="37"/>
       <c r="AG41" s="20"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="92"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="98"/>
+      <c r="C42" s="85"/>
       <c r="D42" s="36"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -2765,17 +2784,15 @@
       <c r="H42" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="48" t="s">
-        <v>23</v>
-      </c>
+      <c r="I42" s="102"/>
+      <c r="J42" s="102"/>
       <c r="K42" s="36"/>
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" s="36"/>
-      <c r="O42" s="36"/>
+      <c r="O42" s="48" t="s">
+        <v>23</v>
+      </c>
       <c r="P42" s="48" t="s">
         <v>23</v>
       </c>
@@ -2804,19 +2821,19 @@
       <c r="AC42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD42" s="68" t="s">
+      <c r="AD42" s="105"/>
+      <c r="AE42" s="63">
+        <v>10794</v>
+      </c>
+      <c r="AF42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AE42" s="63">
-        <v>10794</v>
-      </c>
-      <c r="AF42" s="36"/>
       <c r="AG42" s="17"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
-      <c r="B43" s="89"/>
-      <c r="C43" s="92"/>
+      <c r="A43" s="90"/>
+      <c r="B43" s="98"/>
+      <c r="C43" s="85"/>
       <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -2824,17 +2841,15 @@
       <c r="H43" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" s="48" t="s">
-        <v>23</v>
-      </c>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
       <c r="K43" s="36"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="36"/>
-      <c r="O43" s="36"/>
+      <c r="O43" s="48" t="s">
+        <v>23</v>
+      </c>
       <c r="P43" s="48" t="s">
         <v>23</v>
       </c>
@@ -2863,19 +2878,19 @@
       <c r="AC43" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD43" s="68" t="s">
+      <c r="AD43" s="105"/>
+      <c r="AE43" s="63">
+        <v>10794</v>
+      </c>
+      <c r="AF43" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AE43" s="63">
-        <v>10794</v>
-      </c>
-      <c r="AF43" s="36"/>
       <c r="AG43" s="17"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="92"/>
+      <c r="A44" s="90"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="85"/>
       <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -2883,17 +2898,15 @@
       <c r="H44" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="48" t="s">
-        <v>23</v>
-      </c>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
       <c r="K44" s="36"/>
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
+      <c r="O44" s="48" t="s">
+        <v>23</v>
+      </c>
       <c r="P44" s="48" t="s">
         <v>23</v>
       </c>
@@ -2922,26 +2935,28 @@
       <c r="AC44" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD44" s="68" t="s">
+      <c r="AD44" s="105"/>
+      <c r="AE44" s="63">
+        <v>10794</v>
+      </c>
+      <c r="AF44" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AE44" s="63">
-        <v>10794</v>
-      </c>
-      <c r="AF44" s="36"/>
       <c r="AG44" s="17"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="86"/>
-      <c r="B45" s="90" t="s">
+      <c r="A45" s="90"/>
+      <c r="B45" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="92"/>
+      <c r="C45" s="85"/>
       <c r="D45" s="32"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
       <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
+      <c r="H45" s="48" t="s">
+        <v>23</v>
+      </c>
       <c r="I45" s="32"/>
       <c r="J45" s="32"/>
       <c r="K45" s="32"/>
@@ -2949,7 +2964,9 @@
       <c r="M45" s="18"/>
       <c r="N45" s="32"/>
       <c r="O45" s="32"/>
-      <c r="P45" s="32"/>
+      <c r="P45" s="63">
+        <v>10794</v>
+      </c>
       <c r="Q45" s="63">
         <v>10794</v>
       </c>
@@ -2975,24 +2992,26 @@
       <c r="AC45" s="63">
         <v>10794</v>
       </c>
-      <c r="AD45" s="68" t="s">
+      <c r="AD45" s="105"/>
+      <c r="AE45" s="63">
+        <v>10794</v>
+      </c>
+      <c r="AF45" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AE45" s="63">
-        <v>10794</v>
-      </c>
-      <c r="AF45" s="32"/>
       <c r="AG45" s="18"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="86"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="92"/>
+      <c r="A46" s="90"/>
+      <c r="B46" s="98"/>
+      <c r="C46" s="85"/>
       <c r="D46" s="32"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
       <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
+      <c r="H46" s="48" t="s">
+        <v>23</v>
+      </c>
       <c r="I46" s="32"/>
       <c r="J46" s="32"/>
       <c r="K46" s="32"/>
@@ -3000,7 +3019,9 @@
       <c r="M46" s="19"/>
       <c r="N46" s="32"/>
       <c r="O46" s="32"/>
-      <c r="P46" s="32"/>
+      <c r="P46" s="63">
+        <v>10794</v>
+      </c>
       <c r="Q46" s="63">
         <v>10794</v>
       </c>
@@ -3030,18 +3051,22 @@
       <c r="AE46" s="63">
         <v>10794</v>
       </c>
-      <c r="AF46" s="32"/>
+      <c r="AF46" s="68" t="s">
+        <v>25</v>
+      </c>
       <c r="AG46" s="19"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="87"/>
-      <c r="B47" s="91"/>
-      <c r="C47" s="100"/>
+      <c r="A47" s="91"/>
+      <c r="B47" s="100"/>
+      <c r="C47" s="96"/>
       <c r="D47" s="34"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
       <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
+      <c r="H47" s="48" t="s">
+        <v>23</v>
+      </c>
       <c r="I47" s="34"/>
       <c r="J47" s="34"/>
       <c r="K47" s="34"/>
@@ -3049,7 +3074,9 @@
       <c r="M47" s="21"/>
       <c r="N47" s="34"/>
       <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
+      <c r="P47" s="64">
+        <v>10794</v>
+      </c>
       <c r="Q47" s="64">
         <v>10794</v>
       </c>
@@ -3083,10 +3110,10 @@
       <c r="AG47" s="21"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="85">
+      <c r="A48" s="89">
         <v>46054</v>
       </c>
-      <c r="B48" s="88" t="s">
+      <c r="B48" s="99" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="39"/>
@@ -3115,7 +3142,7 @@
       <c r="P48" s="39"/>
       <c r="Q48" s="39"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="93" t="s">
+      <c r="S48" s="86" t="s">
         <v>26</v>
       </c>
       <c r="T48" s="82">
@@ -3142,8 +3169,8 @@
       <c r="AG48" s="43"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="86"/>
-      <c r="B49" s="89"/>
+      <c r="A49" s="90"/>
+      <c r="B49" s="98"/>
       <c r="C49" s="40"/>
       <c r="D49" s="36"/>
       <c r="E49" s="68" t="s">
@@ -3170,7 +3197,7 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="36"/>
-      <c r="S49" s="94"/>
+      <c r="S49" s="87"/>
       <c r="T49" s="67">
         <v>5425</v>
       </c>
@@ -3195,8 +3222,8 @@
       <c r="AG49" s="44"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="86"/>
-      <c r="B50" s="89"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="98"/>
       <c r="C50" s="40"/>
       <c r="D50" s="36"/>
       <c r="E50" s="68" t="s">
@@ -3223,7 +3250,7 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="36"/>
-      <c r="S50" s="94"/>
+      <c r="S50" s="87"/>
       <c r="T50" s="67">
         <v>5425</v>
       </c>
@@ -3248,8 +3275,8 @@
       <c r="AG50" s="44"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="86"/>
-      <c r="B51" s="89"/>
+      <c r="A51" s="90"/>
+      <c r="B51" s="98"/>
       <c r="C51" s="40"/>
       <c r="D51" s="36"/>
       <c r="E51" s="68" t="s">
@@ -3276,7 +3303,7 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="36"/>
-      <c r="S51" s="94"/>
+      <c r="S51" s="87"/>
       <c r="T51" s="67">
         <v>5425</v>
       </c>
@@ -3301,8 +3328,8 @@
       <c r="AG51" s="44"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="86"/>
-      <c r="B52" s="90" t="s">
+      <c r="A52" s="90"/>
+      <c r="B52" s="97" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="41"/>
@@ -3331,7 +3358,7 @@
       <c r="P52" s="41"/>
       <c r="Q52" s="41"/>
       <c r="R52" s="32"/>
-      <c r="S52" s="94"/>
+      <c r="S52" s="87"/>
       <c r="T52" s="67">
         <v>5425</v>
       </c>
@@ -3356,8 +3383,8 @@
       <c r="AG52" s="45"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="86"/>
-      <c r="B53" s="89"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="98"/>
       <c r="C53" s="41"/>
       <c r="D53" s="32"/>
       <c r="E53" s="63">
@@ -3384,7 +3411,7 @@
       <c r="P53" s="41"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="32"/>
-      <c r="S53" s="94"/>
+      <c r="S53" s="87"/>
       <c r="T53" s="67">
         <v>5425</v>
       </c>
@@ -3409,8 +3436,8 @@
       <c r="AG53" s="45"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="87"/>
-      <c r="B54" s="91"/>
+      <c r="A54" s="91"/>
+      <c r="B54" s="100"/>
       <c r="C54" s="42"/>
       <c r="D54" s="34"/>
       <c r="E54" s="64">
@@ -3437,7 +3464,7 @@
       <c r="P54" s="42"/>
       <c r="Q54" s="42"/>
       <c r="R54" s="34"/>
-      <c r="S54" s="95"/>
+      <c r="S54" s="88"/>
       <c r="T54" s="34"/>
       <c r="U54" s="83">
         <v>5425</v>
@@ -3461,6 +3488,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3477,12 +3509,8 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
   </mergeCells>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="C6" numberStoredAsText="1"/>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489BB710-5B00-4738-9611-75A213742E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67628CD-D353-424E-AA1C-A08E39AB8457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="29">
   <si>
     <t>Código</t>
   </si>
@@ -119,6 +119,9 @@
   <si>
     <t>Feito</t>
   </si>
+  <si>
+    <t>Aprovado</t>
+  </si>
 </sst>
 </file>
 
@@ -127,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +242,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -646,7 +656,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -868,6 +878,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="16" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -880,15 +926,6 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -904,33 +941,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="15" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="15" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="15" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="16" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="15" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Euro" xfId="2" xr:uid="{DD3A81DB-1FA7-4E0F-9A23-1484AF7F90C2}"/>
@@ -1263,12 +1274,13 @@
   <cols>
     <col min="4" max="4" width="58.5703125" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D1" s="14"/>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C5" s="2">
         <v>5089</v>
       </c>
@@ -1295,8 +1307,11 @@
       <c r="F5" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="106" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1310,7 +1325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C7" s="4">
         <v>10789</v>
       </c>
@@ -1323,8 +1338,11 @@
       <c r="F7" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="106" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C8" s="5">
         <v>5409</v>
       </c>
@@ -1338,7 +1356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C9" s="6">
         <v>10793</v>
       </c>
@@ -1351,8 +1369,11 @@
       <c r="F9" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="106" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C10" s="7">
         <v>10788</v>
       </c>
@@ -1366,7 +1387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C11" s="8">
         <v>10794</v>
       </c>
@@ -1380,7 +1401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C12" s="9">
         <v>10790</v>
       </c>
@@ -1394,7 +1415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C13" s="10">
         <v>10795</v>
       </c>
@@ -1405,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C14" s="11">
         <v>5425</v>
       </c>
@@ -1514,17 +1535,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="89">
+      <c r="A20" s="90">
         <v>45931</v>
       </c>
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="93" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
       <c r="E20" s="26"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="92" t="s">
+      <c r="G20" s="101" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="28"/>
@@ -1583,13 +1604,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="90"/>
-      <c r="B21" s="98"/>
+      <c r="A21" s="91"/>
+      <c r="B21" s="94"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="22"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="93"/>
+      <c r="G21" s="102"/>
       <c r="H21" s="29"/>
       <c r="I21" s="51"/>
       <c r="J21" s="57">
@@ -1646,13 +1667,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="90"/>
-      <c r="B22" s="98"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="94"/>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="22"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="93"/>
+      <c r="G22" s="102"/>
       <c r="H22" s="29"/>
       <c r="I22" s="51"/>
       <c r="J22" s="57">
@@ -1709,13 +1730,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="90"/>
-      <c r="B23" s="98"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="22"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="93"/>
+      <c r="G23" s="102"/>
       <c r="H23" s="29"/>
       <c r="I23" s="51"/>
       <c r="J23" s="52"/>
@@ -1770,15 +1791,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="90"/>
-      <c r="B24" s="97" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="93"/>
+      <c r="G24" s="102"/>
       <c r="H24" s="32"/>
       <c r="I24" s="51"/>
       <c r="J24" s="57">
@@ -1833,13 +1854,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="90"/>
-      <c r="B25" s="98"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="93"/>
+      <c r="G25" s="102"/>
       <c r="H25" s="32"/>
       <c r="I25" s="51"/>
       <c r="J25" s="57">
@@ -1894,13 +1915,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91"/>
-      <c r="B26" s="100"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
       <c r="E26" s="55"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="94"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="34"/>
       <c r="I26" s="55"/>
       <c r="J26" s="58">
@@ -1955,10 +1976,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="89">
+      <c r="A27" s="90">
         <v>45962</v>
       </c>
-      <c r="B27" s="99" t="s">
+      <c r="B27" s="93" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2026,8 +2047,8 @@
       <c r="AG27" s="27"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="90"/>
-      <c r="B28" s="98"/>
+      <c r="A28" s="91"/>
+      <c r="B28" s="94"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="49" t="s">
@@ -2093,8 +2114,8 @@
       <c r="AG28" s="25"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="90"/>
-      <c r="B29" s="98"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="94"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="49" t="s">
@@ -2160,8 +2181,8 @@
       <c r="AG29" s="25"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="90"/>
-      <c r="B30" s="98"/>
+      <c r="A30" s="91"/>
+      <c r="B30" s="94"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="49" t="s">
@@ -2227,8 +2248,8 @@
       <c r="AG30" s="25"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="90"/>
-      <c r="B31" s="97" t="s">
+      <c r="A31" s="91"/>
+      <c r="B31" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="18"/>
@@ -2280,8 +2301,8 @@
       <c r="AG31" s="25"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="90"/>
-      <c r="B32" s="98"/>
+      <c r="A32" s="91"/>
+      <c r="B32" s="94"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="51"/>
@@ -2331,8 +2352,8 @@
       <c r="AG32" s="25"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
-      <c r="B33" s="100"/>
+      <c r="A33" s="92"/>
+      <c r="B33" s="96"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
       <c r="E33" s="55"/>
@@ -2382,13 +2403,13 @@
       <c r="AG33" s="35"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="90">
+      <c r="A34" s="91">
         <v>45992</v>
       </c>
-      <c r="B34" s="98" t="s">
+      <c r="B34" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="97" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="69" t="s">
@@ -2403,7 +2424,7 @@
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="85" t="s">
+      <c r="J34" s="97" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="69" t="s">
@@ -2428,7 +2449,7 @@
       <c r="X34" s="36"/>
       <c r="Y34" s="36"/>
       <c r="Z34" s="36"/>
-      <c r="AA34" s="85" t="s">
+      <c r="AA34" s="97" t="s">
         <v>24</v>
       </c>
       <c r="AB34" s="36"/>
@@ -2439,9 +2460,9 @@
       <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="90"/>
-      <c r="B35" s="98"/>
-      <c r="C35" s="85"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="97"/>
       <c r="D35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2454,7 +2475,7 @@
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="85"/>
+      <c r="J35" s="97"/>
       <c r="K35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2477,7 +2498,7 @@
       <c r="X35" s="36"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
-      <c r="AA35" s="85"/>
+      <c r="AA35" s="97"/>
       <c r="AB35" s="36"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
@@ -2486,9 +2507,9 @@
       <c r="AG35" s="36"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="90"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="85"/>
+      <c r="A36" s="91"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="97"/>
       <c r="D36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2501,7 +2522,7 @@
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-      <c r="J36" s="85"/>
+      <c r="J36" s="97"/>
       <c r="K36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2524,7 +2545,7 @@
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="85"/>
+      <c r="AA36" s="97"/>
       <c r="AB36" s="36"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
@@ -2533,9 +2554,9 @@
       <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="90"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="85"/>
+      <c r="A37" s="91"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="97"/>
       <c r="D37" s="47" t="s">
         <v>22</v>
       </c>
@@ -2548,7 +2569,7 @@
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="85"/>
+      <c r="J37" s="97"/>
       <c r="K37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2571,7 +2592,7 @@
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
-      <c r="AA37" s="85"/>
+      <c r="AA37" s="97"/>
       <c r="AB37" s="36"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
@@ -2580,11 +2601,11 @@
       <c r="AG37" s="36"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="90"/>
-      <c r="B38" s="97" t="s">
+      <c r="A38" s="91"/>
+      <c r="B38" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="85"/>
+      <c r="C38" s="97"/>
       <c r="D38" s="53"/>
       <c r="E38" s="60">
         <v>10793</v>
@@ -2595,7 +2616,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="85"/>
+      <c r="J38" s="97"/>
       <c r="K38" s="53"/>
       <c r="L38" s="63">
         <v>10794</v>
@@ -2616,7 +2637,7 @@
       <c r="X38" s="32"/>
       <c r="Y38" s="32"/>
       <c r="Z38" s="32"/>
-      <c r="AA38" s="85"/>
+      <c r="AA38" s="97"/>
       <c r="AB38" s="32"/>
       <c r="AC38" s="18"/>
       <c r="AD38" s="18"/>
@@ -2625,9 +2646,9 @@
       <c r="AG38" s="32"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="90"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="85"/>
+      <c r="A39" s="91"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="97"/>
       <c r="D39" s="53"/>
       <c r="E39" s="60">
         <v>10793</v>
@@ -2638,7 +2659,7 @@
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="85"/>
+      <c r="J39" s="97"/>
       <c r="K39" s="53"/>
       <c r="L39" s="63">
         <v>10794</v>
@@ -2659,7 +2680,7 @@
       <c r="X39" s="32"/>
       <c r="Y39" s="32"/>
       <c r="Z39" s="32"/>
-      <c r="AA39" s="85"/>
+      <c r="AA39" s="97"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="19"/>
       <c r="AD39" s="19"/>
@@ -2668,9 +2689,9 @@
       <c r="AG39" s="32"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="90"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="85"/>
+      <c r="A40" s="91"/>
+      <c r="B40" s="94"/>
+      <c r="C40" s="97"/>
       <c r="D40" s="56"/>
       <c r="E40" s="60">
         <v>10793</v>
@@ -2681,7 +2702,7 @@
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
-      <c r="J40" s="85"/>
+      <c r="J40" s="97"/>
       <c r="K40" s="54"/>
       <c r="L40" s="66">
         <v>10794</v>
@@ -2702,7 +2723,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="54"/>
       <c r="Z40" s="54"/>
-      <c r="AA40" s="85"/>
+      <c r="AA40" s="97"/>
       <c r="AB40" s="54"/>
       <c r="AC40" s="33"/>
       <c r="AD40" s="33"/>
@@ -2711,13 +2732,13 @@
       <c r="AG40" s="54"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="89">
+      <c r="A41" s="90">
         <v>46023</v>
       </c>
-      <c r="B41" s="99" t="s">
+      <c r="B41" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="95" t="s">
+      <c r="C41" s="104" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37"/>
@@ -2727,8 +2748,8 @@
       <c r="H41" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="101"/>
-      <c r="J41" s="101"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="85"/>
       <c r="K41" s="37"/>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
@@ -2742,7 +2763,7 @@
       <c r="Q41" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="R41" s="104" t="s">
+      <c r="R41" s="88" t="s">
         <v>23</v>
       </c>
       <c r="S41" s="20"/>
@@ -2764,7 +2785,7 @@
       <c r="AC41" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AD41" s="103"/>
+      <c r="AD41" s="87"/>
       <c r="AE41" s="65">
         <v>10794</v>
       </c>
@@ -2774,9 +2795,9 @@
       <c r="AG41" s="20"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="90"/>
-      <c r="B42" s="98"/>
-      <c r="C42" s="85"/>
+      <c r="A42" s="91"/>
+      <c r="B42" s="94"/>
+      <c r="C42" s="97"/>
       <c r="D42" s="36"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -2784,8 +2805,8 @@
       <c r="H42" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
+      <c r="I42" s="86"/>
+      <c r="J42" s="86"/>
       <c r="K42" s="36"/>
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
@@ -2821,7 +2842,7 @@
       <c r="AC42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD42" s="105"/>
+      <c r="AD42" s="89"/>
       <c r="AE42" s="63">
         <v>10794</v>
       </c>
@@ -2831,9 +2852,9 @@
       <c r="AG42" s="17"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="90"/>
-      <c r="B43" s="98"/>
-      <c r="C43" s="85"/>
+      <c r="A43" s="91"/>
+      <c r="B43" s="94"/>
+      <c r="C43" s="97"/>
       <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -2841,8 +2862,8 @@
       <c r="H43" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="102"/>
-      <c r="J43" s="102"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
       <c r="K43" s="36"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
@@ -2878,7 +2899,7 @@
       <c r="AC43" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD43" s="105"/>
+      <c r="AD43" s="89"/>
       <c r="AE43" s="63">
         <v>10794</v>
       </c>
@@ -2888,9 +2909,9 @@
       <c r="AG43" s="17"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="90"/>
-      <c r="B44" s="98"/>
-      <c r="C44" s="85"/>
+      <c r="A44" s="91"/>
+      <c r="B44" s="94"/>
+      <c r="C44" s="97"/>
       <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -2898,8 +2919,8 @@
       <c r="H44" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="102"/>
-      <c r="J44" s="102"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
       <c r="K44" s="36"/>
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
@@ -2935,7 +2956,7 @@
       <c r="AC44" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD44" s="105"/>
+      <c r="AD44" s="89"/>
       <c r="AE44" s="63">
         <v>10794</v>
       </c>
@@ -2945,11 +2966,11 @@
       <c r="AG44" s="17"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="90"/>
-      <c r="B45" s="97" t="s">
+      <c r="A45" s="91"/>
+      <c r="B45" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="85"/>
+      <c r="C45" s="97"/>
       <c r="D45" s="32"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -2992,7 +3013,7 @@
       <c r="AC45" s="63">
         <v>10794</v>
       </c>
-      <c r="AD45" s="105"/>
+      <c r="AD45" s="89"/>
       <c r="AE45" s="63">
         <v>10794</v>
       </c>
@@ -3002,9 +3023,9 @@
       <c r="AG45" s="18"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="90"/>
-      <c r="B46" s="98"/>
-      <c r="C46" s="85"/>
+      <c r="A46" s="91"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="97"/>
       <c r="D46" s="32"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
@@ -3057,9 +3078,9 @@
       <c r="AG46" s="19"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="91"/>
-      <c r="B47" s="100"/>
-      <c r="C47" s="96"/>
+      <c r="A47" s="92"/>
+      <c r="B47" s="96"/>
+      <c r="C47" s="105"/>
       <c r="D47" s="34"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
@@ -3110,10 +3131,10 @@
       <c r="AG47" s="21"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="89">
+      <c r="A48" s="90">
         <v>46054</v>
       </c>
-      <c r="B48" s="99" t="s">
+      <c r="B48" s="93" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="39"/>
@@ -3142,7 +3163,7 @@
       <c r="P48" s="39"/>
       <c r="Q48" s="39"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="86" t="s">
+      <c r="S48" s="98" t="s">
         <v>26</v>
       </c>
       <c r="T48" s="82">
@@ -3169,8 +3190,8 @@
       <c r="AG48" s="43"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="90"/>
-      <c r="B49" s="98"/>
+      <c r="A49" s="91"/>
+      <c r="B49" s="94"/>
       <c r="C49" s="40"/>
       <c r="D49" s="36"/>
       <c r="E49" s="68" t="s">
@@ -3197,7 +3218,7 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="36"/>
-      <c r="S49" s="87"/>
+      <c r="S49" s="99"/>
       <c r="T49" s="67">
         <v>5425</v>
       </c>
@@ -3222,8 +3243,8 @@
       <c r="AG49" s="44"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="90"/>
-      <c r="B50" s="98"/>
+      <c r="A50" s="91"/>
+      <c r="B50" s="94"/>
       <c r="C50" s="40"/>
       <c r="D50" s="36"/>
       <c r="E50" s="68" t="s">
@@ -3250,7 +3271,7 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="36"/>
-      <c r="S50" s="87"/>
+      <c r="S50" s="99"/>
       <c r="T50" s="67">
         <v>5425</v>
       </c>
@@ -3275,8 +3296,8 @@
       <c r="AG50" s="44"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="90"/>
-      <c r="B51" s="98"/>
+      <c r="A51" s="91"/>
+      <c r="B51" s="94"/>
       <c r="C51" s="40"/>
       <c r="D51" s="36"/>
       <c r="E51" s="68" t="s">
@@ -3303,7 +3324,7 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="36"/>
-      <c r="S51" s="87"/>
+      <c r="S51" s="99"/>
       <c r="T51" s="67">
         <v>5425</v>
       </c>
@@ -3328,8 +3349,8 @@
       <c r="AG51" s="44"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="90"/>
-      <c r="B52" s="97" t="s">
+      <c r="A52" s="91"/>
+      <c r="B52" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="41"/>
@@ -3358,7 +3379,7 @@
       <c r="P52" s="41"/>
       <c r="Q52" s="41"/>
       <c r="R52" s="32"/>
-      <c r="S52" s="87"/>
+      <c r="S52" s="99"/>
       <c r="T52" s="67">
         <v>5425</v>
       </c>
@@ -3383,8 +3404,8 @@
       <c r="AG52" s="45"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="90"/>
-      <c r="B53" s="98"/>
+      <c r="A53" s="91"/>
+      <c r="B53" s="94"/>
       <c r="C53" s="41"/>
       <c r="D53" s="32"/>
       <c r="E53" s="63">
@@ -3411,7 +3432,7 @@
       <c r="P53" s="41"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="32"/>
-      <c r="S53" s="87"/>
+      <c r="S53" s="99"/>
       <c r="T53" s="67">
         <v>5425</v>
       </c>
@@ -3436,8 +3457,8 @@
       <c r="AG53" s="45"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="91"/>
-      <c r="B54" s="100"/>
+      <c r="A54" s="92"/>
+      <c r="B54" s="96"/>
       <c r="C54" s="42"/>
       <c r="D54" s="34"/>
       <c r="E54" s="64">
@@ -3464,7 +3485,7 @@
       <c r="P54" s="42"/>
       <c r="Q54" s="42"/>
       <c r="R54" s="34"/>
-      <c r="S54" s="88"/>
+      <c r="S54" s="100"/>
       <c r="T54" s="34"/>
       <c r="U54" s="83">
         <v>5425</v>
@@ -3488,11 +3509,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3509,6 +3525,11 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67628CD-D353-424E-AA1C-A08E39AB8457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BE22D3-AA6D-4F70-AB88-26A5EED2F65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="30">
   <si>
     <t>Código</t>
   </si>
@@ -117,10 +117,13 @@
     <t>Carnaval</t>
   </si>
   <si>
-    <t>Feito</t>
+    <t>Aprovado</t>
   </si>
   <si>
-    <t>Aprovado</t>
+    <t>Fazer Jogo DVD</t>
+  </si>
+  <si>
+    <t>Forms Cruzados</t>
   </si>
 </sst>
 </file>
@@ -893,27 +896,7 @@
     <xf numFmtId="49" fontId="6" fillId="15" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -926,6 +909,15 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -941,7 +933,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Euro" xfId="2" xr:uid="{DD3A81DB-1FA7-4E0F-9A23-1484AF7F90C2}"/>
@@ -1307,8 +1310,8 @@
       <c r="F5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="106" t="s">
-        <v>28</v>
+      <c r="G5" s="90" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.25">
@@ -1338,8 +1341,8 @@
       <c r="F7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="106" t="s">
-        <v>28</v>
+      <c r="G7" s="90" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.25">
@@ -1369,8 +1372,8 @@
       <c r="F9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="106" t="s">
-        <v>28</v>
+      <c r="G9" s="90" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="3:7" x14ac:dyDescent="0.25">
@@ -1398,7 +1401,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="3:7" x14ac:dyDescent="0.25">
@@ -1412,7 +1415,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="84" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="3:7" x14ac:dyDescent="0.25">
@@ -1535,17 +1538,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="90">
+      <c r="A20" s="95">
         <v>45931</v>
       </c>
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
       <c r="E20" s="26"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="101" t="s">
+      <c r="G20" s="98" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="28"/>
@@ -1604,13 +1607,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="91"/>
-      <c r="B21" s="94"/>
+      <c r="A21" s="96"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="22"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="102"/>
+      <c r="G21" s="99"/>
       <c r="H21" s="29"/>
       <c r="I21" s="51"/>
       <c r="J21" s="57">
@@ -1667,13 +1670,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="91"/>
-      <c r="B22" s="94"/>
+      <c r="A22" s="96"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="22"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="102"/>
+      <c r="G22" s="99"/>
       <c r="H22" s="29"/>
       <c r="I22" s="51"/>
       <c r="J22" s="57">
@@ -1730,13 +1733,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="91"/>
-      <c r="B23" s="94"/>
+      <c r="A23" s="96"/>
+      <c r="B23" s="104"/>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="22"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="102"/>
+      <c r="G23" s="99"/>
       <c r="H23" s="29"/>
       <c r="I23" s="51"/>
       <c r="J23" s="52"/>
@@ -1791,15 +1794,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="91"/>
-      <c r="B24" s="95" t="s">
+      <c r="A24" s="96"/>
+      <c r="B24" s="103" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="102"/>
+      <c r="G24" s="99"/>
       <c r="H24" s="32"/>
       <c r="I24" s="51"/>
       <c r="J24" s="57">
@@ -1854,13 +1857,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="91"/>
-      <c r="B25" s="94"/>
+      <c r="A25" s="96"/>
+      <c r="B25" s="104"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="102"/>
+      <c r="G25" s="99"/>
       <c r="H25" s="32"/>
       <c r="I25" s="51"/>
       <c r="J25" s="57">
@@ -1915,13 +1918,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
-      <c r="B26" s="96"/>
+      <c r="A26" s="97"/>
+      <c r="B26" s="106"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
       <c r="E26" s="55"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="103"/>
+      <c r="G26" s="100"/>
       <c r="H26" s="34"/>
       <c r="I26" s="55"/>
       <c r="J26" s="58">
@@ -1976,10 +1979,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="90">
+      <c r="A27" s="95">
         <v>45962</v>
       </c>
-      <c r="B27" s="93" t="s">
+      <c r="B27" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2047,8 +2050,8 @@
       <c r="AG27" s="27"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="91"/>
-      <c r="B28" s="94"/>
+      <c r="A28" s="96"/>
+      <c r="B28" s="104"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="49" t="s">
@@ -2114,8 +2117,8 @@
       <c r="AG28" s="25"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="91"/>
-      <c r="B29" s="94"/>
+      <c r="A29" s="96"/>
+      <c r="B29" s="104"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="49" t="s">
@@ -2181,8 +2184,8 @@
       <c r="AG29" s="25"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="91"/>
-      <c r="B30" s="94"/>
+      <c r="A30" s="96"/>
+      <c r="B30" s="104"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="49" t="s">
@@ -2248,8 +2251,8 @@
       <c r="AG30" s="25"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="91"/>
-      <c r="B31" s="95" t="s">
+      <c r="A31" s="96"/>
+      <c r="B31" s="103" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="18"/>
@@ -2301,8 +2304,8 @@
       <c r="AG31" s="25"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="91"/>
-      <c r="B32" s="94"/>
+      <c r="A32" s="96"/>
+      <c r="B32" s="104"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="51"/>
@@ -2352,8 +2355,8 @@
       <c r="AG32" s="25"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="B33" s="96"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="106"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
       <c r="E33" s="55"/>
@@ -2403,13 +2406,13 @@
       <c r="AG33" s="35"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="91">
+      <c r="A34" s="96">
         <v>45992</v>
       </c>
-      <c r="B34" s="94" t="s">
+      <c r="B34" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="97" t="s">
+      <c r="C34" s="91" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="69" t="s">
@@ -2424,7 +2427,7 @@
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="97" t="s">
+      <c r="J34" s="91" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="69" t="s">
@@ -2449,7 +2452,7 @@
       <c r="X34" s="36"/>
       <c r="Y34" s="36"/>
       <c r="Z34" s="36"/>
-      <c r="AA34" s="97" t="s">
+      <c r="AA34" s="91" t="s">
         <v>24</v>
       </c>
       <c r="AB34" s="36"/>
@@ -2460,9 +2463,9 @@
       <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
-      <c r="B35" s="94"/>
-      <c r="C35" s="97"/>
+      <c r="A35" s="96"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="91"/>
       <c r="D35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2475,7 +2478,7 @@
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="97"/>
+      <c r="J35" s="91"/>
       <c r="K35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2498,7 +2501,7 @@
       <c r="X35" s="36"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
-      <c r="AA35" s="97"/>
+      <c r="AA35" s="91"/>
       <c r="AB35" s="36"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
@@ -2507,9 +2510,9 @@
       <c r="AG35" s="36"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="91"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="97"/>
+      <c r="A36" s="96"/>
+      <c r="B36" s="104"/>
+      <c r="C36" s="91"/>
       <c r="D36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2522,7 +2525,7 @@
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-      <c r="J36" s="97"/>
+      <c r="J36" s="91"/>
       <c r="K36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2545,7 +2548,7 @@
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="97"/>
+      <c r="AA36" s="91"/>
       <c r="AB36" s="36"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
@@ -2554,9 +2557,9 @@
       <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="91"/>
-      <c r="B37" s="94"/>
-      <c r="C37" s="97"/>
+      <c r="A37" s="96"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="47" t="s">
         <v>22</v>
       </c>
@@ -2569,7 +2572,7 @@
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="97"/>
+      <c r="J37" s="91"/>
       <c r="K37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2592,7 +2595,7 @@
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
-      <c r="AA37" s="97"/>
+      <c r="AA37" s="91"/>
       <c r="AB37" s="36"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
@@ -2601,11 +2604,11 @@
       <c r="AG37" s="36"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="91"/>
-      <c r="B38" s="95" t="s">
+      <c r="A38" s="96"/>
+      <c r="B38" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="97"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="53"/>
       <c r="E38" s="60">
         <v>10793</v>
@@ -2616,7 +2619,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="97"/>
+      <c r="J38" s="91"/>
       <c r="K38" s="53"/>
       <c r="L38" s="63">
         <v>10794</v>
@@ -2637,7 +2640,7 @@
       <c r="X38" s="32"/>
       <c r="Y38" s="32"/>
       <c r="Z38" s="32"/>
-      <c r="AA38" s="97"/>
+      <c r="AA38" s="91"/>
       <c r="AB38" s="32"/>
       <c r="AC38" s="18"/>
       <c r="AD38" s="18"/>
@@ -2646,9 +2649,9 @@
       <c r="AG38" s="32"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="91"/>
-      <c r="B39" s="94"/>
-      <c r="C39" s="97"/>
+      <c r="A39" s="96"/>
+      <c r="B39" s="104"/>
+      <c r="C39" s="91"/>
       <c r="D39" s="53"/>
       <c r="E39" s="60">
         <v>10793</v>
@@ -2659,7 +2662,7 @@
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="97"/>
+      <c r="J39" s="91"/>
       <c r="K39" s="53"/>
       <c r="L39" s="63">
         <v>10794</v>
@@ -2680,7 +2683,7 @@
       <c r="X39" s="32"/>
       <c r="Y39" s="32"/>
       <c r="Z39" s="32"/>
-      <c r="AA39" s="97"/>
+      <c r="AA39" s="91"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="19"/>
       <c r="AD39" s="19"/>
@@ -2689,9 +2692,9 @@
       <c r="AG39" s="32"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="91"/>
-      <c r="B40" s="94"/>
-      <c r="C40" s="97"/>
+      <c r="A40" s="96"/>
+      <c r="B40" s="104"/>
+      <c r="C40" s="91"/>
       <c r="D40" s="56"/>
       <c r="E40" s="60">
         <v>10793</v>
@@ -2702,7 +2705,7 @@
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
-      <c r="J40" s="97"/>
+      <c r="J40" s="91"/>
       <c r="K40" s="54"/>
       <c r="L40" s="66">
         <v>10794</v>
@@ -2723,7 +2726,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="54"/>
       <c r="Z40" s="54"/>
-      <c r="AA40" s="97"/>
+      <c r="AA40" s="91"/>
       <c r="AB40" s="54"/>
       <c r="AC40" s="33"/>
       <c r="AD40" s="33"/>
@@ -2732,13 +2735,13 @@
       <c r="AG40" s="54"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="90">
+      <c r="A41" s="95">
         <v>46023</v>
       </c>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="104" t="s">
+      <c r="C41" s="101" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37"/>
@@ -2795,9 +2798,9 @@
       <c r="AG41" s="20"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="91"/>
-      <c r="B42" s="94"/>
-      <c r="C42" s="97"/>
+      <c r="A42" s="96"/>
+      <c r="B42" s="104"/>
+      <c r="C42" s="91"/>
       <c r="D42" s="36"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -2852,9 +2855,9 @@
       <c r="AG42" s="17"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="91"/>
-      <c r="B43" s="94"/>
-      <c r="C43" s="97"/>
+      <c r="A43" s="96"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="91"/>
       <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -2909,9 +2912,9 @@
       <c r="AG43" s="17"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="91"/>
-      <c r="B44" s="94"/>
-      <c r="C44" s="97"/>
+      <c r="A44" s="96"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="91"/>
       <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -2966,11 +2969,11 @@
       <c r="AG44" s="17"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="91"/>
-      <c r="B45" s="95" t="s">
+      <c r="A45" s="96"/>
+      <c r="B45" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="97"/>
+      <c r="C45" s="91"/>
       <c r="D45" s="32"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -3023,9 +3026,9 @@
       <c r="AG45" s="18"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="91"/>
-      <c r="B46" s="94"/>
-      <c r="C46" s="97"/>
+      <c r="A46" s="96"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="91"/>
       <c r="D46" s="32"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
@@ -3078,9 +3081,9 @@
       <c r="AG46" s="19"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="92"/>
-      <c r="B47" s="96"/>
-      <c r="C47" s="105"/>
+      <c r="A47" s="97"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="102"/>
       <c r="D47" s="34"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
@@ -3131,10 +3134,10 @@
       <c r="AG47" s="21"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="90">
+      <c r="A48" s="95">
         <v>46054</v>
       </c>
-      <c r="B48" s="93" t="s">
+      <c r="B48" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="39"/>
@@ -3163,7 +3166,7 @@
       <c r="P48" s="39"/>
       <c r="Q48" s="39"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="98" t="s">
+      <c r="S48" s="92" t="s">
         <v>26</v>
       </c>
       <c r="T48" s="82">
@@ -3190,8 +3193,8 @@
       <c r="AG48" s="43"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="91"/>
-      <c r="B49" s="94"/>
+      <c r="A49" s="96"/>
+      <c r="B49" s="104"/>
       <c r="C49" s="40"/>
       <c r="D49" s="36"/>
       <c r="E49" s="68" t="s">
@@ -3218,7 +3221,7 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="36"/>
-      <c r="S49" s="99"/>
+      <c r="S49" s="93"/>
       <c r="T49" s="67">
         <v>5425</v>
       </c>
@@ -3243,8 +3246,8 @@
       <c r="AG49" s="44"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="91"/>
-      <c r="B50" s="94"/>
+      <c r="A50" s="96"/>
+      <c r="B50" s="104"/>
       <c r="C50" s="40"/>
       <c r="D50" s="36"/>
       <c r="E50" s="68" t="s">
@@ -3271,7 +3274,7 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="36"/>
-      <c r="S50" s="99"/>
+      <c r="S50" s="93"/>
       <c r="T50" s="67">
         <v>5425</v>
       </c>
@@ -3296,8 +3299,8 @@
       <c r="AG50" s="44"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="91"/>
-      <c r="B51" s="94"/>
+      <c r="A51" s="96"/>
+      <c r="B51" s="104"/>
       <c r="C51" s="40"/>
       <c r="D51" s="36"/>
       <c r="E51" s="68" t="s">
@@ -3324,7 +3327,7 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="36"/>
-      <c r="S51" s="99"/>
+      <c r="S51" s="93"/>
       <c r="T51" s="67">
         <v>5425</v>
       </c>
@@ -3349,8 +3352,8 @@
       <c r="AG51" s="44"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="91"/>
-      <c r="B52" s="95" t="s">
+      <c r="A52" s="96"/>
+      <c r="B52" s="103" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="41"/>
@@ -3379,7 +3382,7 @@
       <c r="P52" s="41"/>
       <c r="Q52" s="41"/>
       <c r="R52" s="32"/>
-      <c r="S52" s="99"/>
+      <c r="S52" s="93"/>
       <c r="T52" s="67">
         <v>5425</v>
       </c>
@@ -3404,8 +3407,8 @@
       <c r="AG52" s="45"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="91"/>
-      <c r="B53" s="94"/>
+      <c r="A53" s="96"/>
+      <c r="B53" s="104"/>
       <c r="C53" s="41"/>
       <c r="D53" s="32"/>
       <c r="E53" s="63">
@@ -3432,7 +3435,7 @@
       <c r="P53" s="41"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="32"/>
-      <c r="S53" s="99"/>
+      <c r="S53" s="93"/>
       <c r="T53" s="67">
         <v>5425</v>
       </c>
@@ -3457,8 +3460,8 @@
       <c r="AG53" s="45"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
-      <c r="B54" s="96"/>
+      <c r="A54" s="97"/>
+      <c r="B54" s="106"/>
       <c r="C54" s="42"/>
       <c r="D54" s="34"/>
       <c r="E54" s="64">
@@ -3485,7 +3488,7 @@
       <c r="P54" s="42"/>
       <c r="Q54" s="42"/>
       <c r="R54" s="34"/>
-      <c r="S54" s="100"/>
+      <c r="S54" s="94"/>
       <c r="T54" s="34"/>
       <c r="U54" s="83">
         <v>5425</v>
@@ -3509,6 +3512,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3525,11 +3533,6 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BE22D3-AA6D-4F70-AB88-26A5EED2F65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5551238B-CF28-40B9-9126-2C08B4BC0458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="29">
   <si>
     <t>Código</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Fazer Jogo DVD</t>
-  </si>
-  <si>
-    <t>Forms Cruzados</t>
   </si>
 </sst>
 </file>
@@ -1414,8 +1411,8 @@
       <c r="E12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="84" t="s">
-        <v>29</v>
+      <c r="F12" s="15" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="3:7" x14ac:dyDescent="0.25">

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5551238B-CF28-40B9-9126-2C08B4BC0458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3382C422-B22A-447F-9E81-3117FEDA27D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="29">
   <si>
     <t>Código</t>
   </si>
@@ -120,7 +120,7 @@
     <t>Aprovado</t>
   </si>
   <si>
-    <t>Fazer Jogo DVD</t>
+    <t>Trabalho Hands-on-Lab</t>
   </si>
 </sst>
 </file>
@@ -130,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,14 +231,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -877,7 +869,6 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="15" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -893,7 +884,28 @@
     <xf numFmtId="49" fontId="6" fillId="15" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -906,15 +918,6 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -930,18 +933,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Euro" xfId="2" xr:uid="{DD3A81DB-1FA7-4E0F-9A23-1484AF7F90C2}"/>
@@ -1273,14 +1265,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="58.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D1" s="14"/>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,7 +1286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" s="2">
         <v>5089</v>
       </c>
@@ -1307,11 +1299,11 @@
       <c r="F5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="90" t="s">
+      <c r="G5" s="89" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" s="4">
         <v>10789</v>
       </c>
@@ -1338,11 +1330,11 @@
       <c r="F7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="90" t="s">
+      <c r="G7" s="89" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5">
         <v>5409</v>
       </c>
@@ -1356,7 +1348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" s="6">
         <v>10793</v>
       </c>
@@ -1369,11 +1361,11 @@
       <c r="F9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="90" t="s">
+      <c r="G9" s="89" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="7">
         <v>10788</v>
       </c>
@@ -1387,7 +1379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" s="8">
         <v>10794</v>
       </c>
@@ -1397,11 +1389,12 @@
       <c r="E11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="84" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="F11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="89"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" s="9">
         <v>10790</v>
       </c>
@@ -1415,7 +1408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" s="10">
         <v>10795</v>
       </c>
@@ -1425,8 +1418,11 @@
       <c r="E13" s="13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="F13" s="106" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" s="11">
         <v>5425</v>
       </c>
@@ -1436,6 +1432,7 @@
       <c r="E14" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="F14" s="6"/>
     </row>
     <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
@@ -1535,17 +1532,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="95">
+      <c r="A20" s="90">
         <v>45931</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="93" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
       <c r="E20" s="26"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="98" t="s">
+      <c r="G20" s="101" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="28"/>
@@ -1604,13 +1601,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="96"/>
-      <c r="B21" s="104"/>
+      <c r="A21" s="91"/>
+      <c r="B21" s="94"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="22"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="99"/>
+      <c r="G21" s="102"/>
       <c r="H21" s="29"/>
       <c r="I21" s="51"/>
       <c r="J21" s="57">
@@ -1667,13 +1664,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="96"/>
-      <c r="B22" s="104"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="94"/>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="22"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="99"/>
+      <c r="G22" s="102"/>
       <c r="H22" s="29"/>
       <c r="I22" s="51"/>
       <c r="J22" s="57">
@@ -1730,13 +1727,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="96"/>
-      <c r="B23" s="104"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="22"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="99"/>
+      <c r="G23" s="102"/>
       <c r="H23" s="29"/>
       <c r="I23" s="51"/>
       <c r="J23" s="52"/>
@@ -1791,15 +1788,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="96"/>
-      <c r="B24" s="103" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="99"/>
+      <c r="G24" s="102"/>
       <c r="H24" s="32"/>
       <c r="I24" s="51"/>
       <c r="J24" s="57">
@@ -1854,13 +1851,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="96"/>
-      <c r="B25" s="104"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="99"/>
+      <c r="G25" s="102"/>
       <c r="H25" s="32"/>
       <c r="I25" s="51"/>
       <c r="J25" s="57">
@@ -1915,13 +1912,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="97"/>
-      <c r="B26" s="106"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
       <c r="E26" s="55"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="100"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="34"/>
       <c r="I26" s="55"/>
       <c r="J26" s="58">
@@ -1976,10 +1973,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="95">
+      <c r="A27" s="90">
         <v>45962</v>
       </c>
-      <c r="B27" s="105" t="s">
+      <c r="B27" s="93" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2047,8 +2044,8 @@
       <c r="AG27" s="27"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="96"/>
-      <c r="B28" s="104"/>
+      <c r="A28" s="91"/>
+      <c r="B28" s="94"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="49" t="s">
@@ -2114,8 +2111,8 @@
       <c r="AG28" s="25"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="96"/>
-      <c r="B29" s="104"/>
+      <c r="A29" s="91"/>
+      <c r="B29" s="94"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="49" t="s">
@@ -2181,8 +2178,8 @@
       <c r="AG29" s="25"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="96"/>
-      <c r="B30" s="104"/>
+      <c r="A30" s="91"/>
+      <c r="B30" s="94"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="49" t="s">
@@ -2248,8 +2245,8 @@
       <c r="AG30" s="25"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="96"/>
-      <c r="B31" s="103" t="s">
+      <c r="A31" s="91"/>
+      <c r="B31" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="18"/>
@@ -2301,8 +2298,8 @@
       <c r="AG31" s="25"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="96"/>
-      <c r="B32" s="104"/>
+      <c r="A32" s="91"/>
+      <c r="B32" s="94"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="51"/>
@@ -2352,8 +2349,8 @@
       <c r="AG32" s="25"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="97"/>
-      <c r="B33" s="106"/>
+      <c r="A33" s="92"/>
+      <c r="B33" s="96"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
       <c r="E33" s="55"/>
@@ -2403,13 +2400,13 @@
       <c r="AG33" s="35"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="96">
+      <c r="A34" s="91">
         <v>45992</v>
       </c>
-      <c r="B34" s="104" t="s">
+      <c r="B34" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="97" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="69" t="s">
@@ -2424,7 +2421,7 @@
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="91" t="s">
+      <c r="J34" s="97" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="69" t="s">
@@ -2449,7 +2446,7 @@
       <c r="X34" s="36"/>
       <c r="Y34" s="36"/>
       <c r="Z34" s="36"/>
-      <c r="AA34" s="91" t="s">
+      <c r="AA34" s="97" t="s">
         <v>24</v>
       </c>
       <c r="AB34" s="36"/>
@@ -2460,9 +2457,9 @@
       <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="96"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="91"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="97"/>
       <c r="D35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2475,7 +2472,7 @@
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="91"/>
+      <c r="J35" s="97"/>
       <c r="K35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2498,7 +2495,7 @@
       <c r="X35" s="36"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
-      <c r="AA35" s="91"/>
+      <c r="AA35" s="97"/>
       <c r="AB35" s="36"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
@@ -2507,9 +2504,9 @@
       <c r="AG35" s="36"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="96"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="91"/>
+      <c r="A36" s="91"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="97"/>
       <c r="D36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2522,7 +2519,7 @@
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-      <c r="J36" s="91"/>
+      <c r="J36" s="97"/>
       <c r="K36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2545,7 +2542,7 @@
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="91"/>
+      <c r="AA36" s="97"/>
       <c r="AB36" s="36"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
@@ -2554,9 +2551,9 @@
       <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="96"/>
-      <c r="B37" s="104"/>
-      <c r="C37" s="91"/>
+      <c r="A37" s="91"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="97"/>
       <c r="D37" s="47" t="s">
         <v>22</v>
       </c>
@@ -2569,7 +2566,7 @@
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="91"/>
+      <c r="J37" s="97"/>
       <c r="K37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2592,7 +2589,7 @@
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
-      <c r="AA37" s="91"/>
+      <c r="AA37" s="97"/>
       <c r="AB37" s="36"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
@@ -2601,11 +2598,11 @@
       <c r="AG37" s="36"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="96"/>
-      <c r="B38" s="103" t="s">
+      <c r="A38" s="91"/>
+      <c r="B38" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="91"/>
+      <c r="C38" s="97"/>
       <c r="D38" s="53"/>
       <c r="E38" s="60">
         <v>10793</v>
@@ -2616,7 +2613,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="91"/>
+      <c r="J38" s="97"/>
       <c r="K38" s="53"/>
       <c r="L38" s="63">
         <v>10794</v>
@@ -2637,7 +2634,7 @@
       <c r="X38" s="32"/>
       <c r="Y38" s="32"/>
       <c r="Z38" s="32"/>
-      <c r="AA38" s="91"/>
+      <c r="AA38" s="97"/>
       <c r="AB38" s="32"/>
       <c r="AC38" s="18"/>
       <c r="AD38" s="18"/>
@@ -2646,9 +2643,9 @@
       <c r="AG38" s="32"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="96"/>
-      <c r="B39" s="104"/>
-      <c r="C39" s="91"/>
+      <c r="A39" s="91"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="97"/>
       <c r="D39" s="53"/>
       <c r="E39" s="60">
         <v>10793</v>
@@ -2659,7 +2656,7 @@
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="91"/>
+      <c r="J39" s="97"/>
       <c r="K39" s="53"/>
       <c r="L39" s="63">
         <v>10794</v>
@@ -2680,7 +2677,7 @@
       <c r="X39" s="32"/>
       <c r="Y39" s="32"/>
       <c r="Z39" s="32"/>
-      <c r="AA39" s="91"/>
+      <c r="AA39" s="97"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="19"/>
       <c r="AD39" s="19"/>
@@ -2689,9 +2686,9 @@
       <c r="AG39" s="32"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96"/>
-      <c r="B40" s="104"/>
-      <c r="C40" s="91"/>
+      <c r="A40" s="91"/>
+      <c r="B40" s="94"/>
+      <c r="C40" s="97"/>
       <c r="D40" s="56"/>
       <c r="E40" s="60">
         <v>10793</v>
@@ -2702,7 +2699,7 @@
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
-      <c r="J40" s="91"/>
+      <c r="J40" s="97"/>
       <c r="K40" s="54"/>
       <c r="L40" s="66">
         <v>10794</v>
@@ -2723,7 +2720,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="54"/>
       <c r="Z40" s="54"/>
-      <c r="AA40" s="91"/>
+      <c r="AA40" s="97"/>
       <c r="AB40" s="54"/>
       <c r="AC40" s="33"/>
       <c r="AD40" s="33"/>
@@ -2732,13 +2729,13 @@
       <c r="AG40" s="54"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="95">
+      <c r="A41" s="90">
         <v>46023</v>
       </c>
-      <c r="B41" s="105" t="s">
+      <c r="B41" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="101" t="s">
+      <c r="C41" s="104" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37"/>
@@ -2748,8 +2745,8 @@
       <c r="H41" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="85"/>
-      <c r="J41" s="85"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
       <c r="K41" s="37"/>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
@@ -2763,7 +2760,7 @@
       <c r="Q41" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="R41" s="88" t="s">
+      <c r="R41" s="87" t="s">
         <v>23</v>
       </c>
       <c r="S41" s="20"/>
@@ -2785,7 +2782,7 @@
       <c r="AC41" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="AD41" s="87"/>
+      <c r="AD41" s="86"/>
       <c r="AE41" s="65">
         <v>10794</v>
       </c>
@@ -2795,9 +2792,9 @@
       <c r="AG41" s="20"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="96"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="91"/>
+      <c r="A42" s="91"/>
+      <c r="B42" s="94"/>
+      <c r="C42" s="97"/>
       <c r="D42" s="36"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -2805,8 +2802,8 @@
       <c r="H42" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="86"/>
-      <c r="J42" s="86"/>
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
       <c r="K42" s="36"/>
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
@@ -2842,7 +2839,7 @@
       <c r="AC42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD42" s="89"/>
+      <c r="AD42" s="88"/>
       <c r="AE42" s="63">
         <v>10794</v>
       </c>
@@ -2852,9 +2849,9 @@
       <c r="AG42" s="17"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="96"/>
-      <c r="B43" s="104"/>
-      <c r="C43" s="91"/>
+      <c r="A43" s="91"/>
+      <c r="B43" s="94"/>
+      <c r="C43" s="97"/>
       <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -2862,8 +2859,8 @@
       <c r="H43" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="86"/>
-      <c r="J43" s="86"/>
+      <c r="I43" s="85"/>
+      <c r="J43" s="85"/>
       <c r="K43" s="36"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
@@ -2899,7 +2896,7 @@
       <c r="AC43" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD43" s="89"/>
+      <c r="AD43" s="88"/>
       <c r="AE43" s="63">
         <v>10794</v>
       </c>
@@ -2909,9 +2906,9 @@
       <c r="AG43" s="17"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="96"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="91"/>
+      <c r="A44" s="91"/>
+      <c r="B44" s="94"/>
+      <c r="C44" s="97"/>
       <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -2919,8 +2916,8 @@
       <c r="H44" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="86"/>
-      <c r="J44" s="86"/>
+      <c r="I44" s="85"/>
+      <c r="J44" s="85"/>
       <c r="K44" s="36"/>
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
@@ -2956,7 +2953,7 @@
       <c r="AC44" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="AD44" s="89"/>
+      <c r="AD44" s="88"/>
       <c r="AE44" s="63">
         <v>10794</v>
       </c>
@@ -2966,11 +2963,11 @@
       <c r="AG44" s="17"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="96"/>
-      <c r="B45" s="103" t="s">
+      <c r="A45" s="91"/>
+      <c r="B45" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="97"/>
       <c r="D45" s="32"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -3013,7 +3010,7 @@
       <c r="AC45" s="63">
         <v>10794</v>
       </c>
-      <c r="AD45" s="89"/>
+      <c r="AD45" s="88"/>
       <c r="AE45" s="63">
         <v>10794</v>
       </c>
@@ -3023,9 +3020,9 @@
       <c r="AG45" s="18"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="96"/>
-      <c r="B46" s="104"/>
-      <c r="C46" s="91"/>
+      <c r="A46" s="91"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="97"/>
       <c r="D46" s="32"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
@@ -3078,9 +3075,9 @@
       <c r="AG46" s="19"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="97"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="102"/>
+      <c r="A47" s="92"/>
+      <c r="B47" s="96"/>
+      <c r="C47" s="105"/>
       <c r="D47" s="34"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
@@ -3131,10 +3128,10 @@
       <c r="AG47" s="21"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="95">
+      <c r="A48" s="90">
         <v>46054</v>
       </c>
-      <c r="B48" s="105" t="s">
+      <c r="B48" s="93" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="39"/>
@@ -3163,7 +3160,7 @@
       <c r="P48" s="39"/>
       <c r="Q48" s="39"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="92" t="s">
+      <c r="S48" s="98" t="s">
         <v>26</v>
       </c>
       <c r="T48" s="82">
@@ -3190,8 +3187,8 @@
       <c r="AG48" s="43"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="96"/>
-      <c r="B49" s="104"/>
+      <c r="A49" s="91"/>
+      <c r="B49" s="94"/>
       <c r="C49" s="40"/>
       <c r="D49" s="36"/>
       <c r="E49" s="68" t="s">
@@ -3218,7 +3215,7 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="36"/>
-      <c r="S49" s="93"/>
+      <c r="S49" s="99"/>
       <c r="T49" s="67">
         <v>5425</v>
       </c>
@@ -3243,8 +3240,8 @@
       <c r="AG49" s="44"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="96"/>
-      <c r="B50" s="104"/>
+      <c r="A50" s="91"/>
+      <c r="B50" s="94"/>
       <c r="C50" s="40"/>
       <c r="D50" s="36"/>
       <c r="E50" s="68" t="s">
@@ -3271,7 +3268,7 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="36"/>
-      <c r="S50" s="93"/>
+      <c r="S50" s="99"/>
       <c r="T50" s="67">
         <v>5425</v>
       </c>
@@ -3296,8 +3293,8 @@
       <c r="AG50" s="44"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="96"/>
-      <c r="B51" s="104"/>
+      <c r="A51" s="91"/>
+      <c r="B51" s="94"/>
       <c r="C51" s="40"/>
       <c r="D51" s="36"/>
       <c r="E51" s="68" t="s">
@@ -3324,7 +3321,7 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="36"/>
-      <c r="S51" s="93"/>
+      <c r="S51" s="99"/>
       <c r="T51" s="67">
         <v>5425</v>
       </c>
@@ -3349,8 +3346,8 @@
       <c r="AG51" s="44"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="96"/>
-      <c r="B52" s="103" t="s">
+      <c r="A52" s="91"/>
+      <c r="B52" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="41"/>
@@ -3379,7 +3376,7 @@
       <c r="P52" s="41"/>
       <c r="Q52" s="41"/>
       <c r="R52" s="32"/>
-      <c r="S52" s="93"/>
+      <c r="S52" s="99"/>
       <c r="T52" s="67">
         <v>5425</v>
       </c>
@@ -3404,8 +3401,8 @@
       <c r="AG52" s="45"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="96"/>
-      <c r="B53" s="104"/>
+      <c r="A53" s="91"/>
+      <c r="B53" s="94"/>
       <c r="C53" s="41"/>
       <c r="D53" s="32"/>
       <c r="E53" s="63">
@@ -3432,7 +3429,7 @@
       <c r="P53" s="41"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="32"/>
-      <c r="S53" s="93"/>
+      <c r="S53" s="99"/>
       <c r="T53" s="67">
         <v>5425</v>
       </c>
@@ -3457,8 +3454,8 @@
       <c r="AG53" s="45"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="97"/>
-      <c r="B54" s="106"/>
+      <c r="A54" s="92"/>
+      <c r="B54" s="96"/>
       <c r="C54" s="42"/>
       <c r="D54" s="34"/>
       <c r="E54" s="64">
@@ -3485,7 +3482,7 @@
       <c r="P54" s="42"/>
       <c r="Q54" s="42"/>
       <c r="R54" s="34"/>
-      <c r="S54" s="94"/>
+      <c r="S54" s="100"/>
       <c r="T54" s="34"/>
       <c r="U54" s="83">
         <v>5425</v>
@@ -3509,11 +3506,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3530,8 +3522,13 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="C6" numberStoredAsText="1"/>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3382C422-B22A-447F-9E81-3117FEDA27D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521FBBE4-46C8-476E-B5EA-466C4F5327EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="30">
   <si>
     <t>Código</t>
   </si>
@@ -120,7 +120,10 @@
     <t>Aprovado</t>
   </si>
   <si>
-    <t>Trabalho Hands-on-Lab</t>
+    <t>TrabalhoFad</t>
+  </si>
+  <si>
+    <t>MinorFixNoSpaceInv</t>
   </si>
 </sst>
 </file>
@@ -885,27 +888,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -918,6 +901,15 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -933,7 +925,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Euro" xfId="2" xr:uid="{DD3A81DB-1FA7-4E0F-9A23-1484AF7F90C2}"/>
@@ -1418,7 +1421,7 @@
       <c r="E13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="106" t="s">
+      <c r="F13" s="90" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1432,7 +1435,9 @@
       <c r="E14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
@@ -1532,17 +1537,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="90">
+      <c r="A20" s="95">
         <v>45931</v>
       </c>
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
       <c r="E20" s="26"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="101" t="s">
+      <c r="G20" s="98" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="28"/>
@@ -1601,13 +1606,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="91"/>
-      <c r="B21" s="94"/>
+      <c r="A21" s="96"/>
+      <c r="B21" s="104"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="22"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="102"/>
+      <c r="G21" s="99"/>
       <c r="H21" s="29"/>
       <c r="I21" s="51"/>
       <c r="J21" s="57">
@@ -1664,13 +1669,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="91"/>
-      <c r="B22" s="94"/>
+      <c r="A22" s="96"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="22"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="102"/>
+      <c r="G22" s="99"/>
       <c r="H22" s="29"/>
       <c r="I22" s="51"/>
       <c r="J22" s="57">
@@ -1727,13 +1732,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="91"/>
-      <c r="B23" s="94"/>
+      <c r="A23" s="96"/>
+      <c r="B23" s="104"/>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="22"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="102"/>
+      <c r="G23" s="99"/>
       <c r="H23" s="29"/>
       <c r="I23" s="51"/>
       <c r="J23" s="52"/>
@@ -1788,15 +1793,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="91"/>
-      <c r="B24" s="95" t="s">
+      <c r="A24" s="96"/>
+      <c r="B24" s="103" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="102"/>
+      <c r="G24" s="99"/>
       <c r="H24" s="32"/>
       <c r="I24" s="51"/>
       <c r="J24" s="57">
@@ -1851,13 +1856,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="91"/>
-      <c r="B25" s="94"/>
+      <c r="A25" s="96"/>
+      <c r="B25" s="104"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="102"/>
+      <c r="G25" s="99"/>
       <c r="H25" s="32"/>
       <c r="I25" s="51"/>
       <c r="J25" s="57">
@@ -1912,13 +1917,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
-      <c r="B26" s="96"/>
+      <c r="A26" s="97"/>
+      <c r="B26" s="106"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
       <c r="E26" s="55"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="103"/>
+      <c r="G26" s="100"/>
       <c r="H26" s="34"/>
       <c r="I26" s="55"/>
       <c r="J26" s="58">
@@ -1973,10 +1978,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="90">
+      <c r="A27" s="95">
         <v>45962</v>
       </c>
-      <c r="B27" s="93" t="s">
+      <c r="B27" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2044,8 +2049,8 @@
       <c r="AG27" s="27"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="91"/>
-      <c r="B28" s="94"/>
+      <c r="A28" s="96"/>
+      <c r="B28" s="104"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="49" t="s">
@@ -2111,8 +2116,8 @@
       <c r="AG28" s="25"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="91"/>
-      <c r="B29" s="94"/>
+      <c r="A29" s="96"/>
+      <c r="B29" s="104"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="49" t="s">
@@ -2178,8 +2183,8 @@
       <c r="AG29" s="25"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="91"/>
-      <c r="B30" s="94"/>
+      <c r="A30" s="96"/>
+      <c r="B30" s="104"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="49" t="s">
@@ -2245,8 +2250,8 @@
       <c r="AG30" s="25"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="91"/>
-      <c r="B31" s="95" t="s">
+      <c r="A31" s="96"/>
+      <c r="B31" s="103" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="18"/>
@@ -2298,8 +2303,8 @@
       <c r="AG31" s="25"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="91"/>
-      <c r="B32" s="94"/>
+      <c r="A32" s="96"/>
+      <c r="B32" s="104"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="51"/>
@@ -2349,8 +2354,8 @@
       <c r="AG32" s="25"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="B33" s="96"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="106"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
       <c r="E33" s="55"/>
@@ -2400,13 +2405,13 @@
       <c r="AG33" s="35"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="91">
+      <c r="A34" s="96">
         <v>45992</v>
       </c>
-      <c r="B34" s="94" t="s">
+      <c r="B34" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="97" t="s">
+      <c r="C34" s="91" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="69" t="s">
@@ -2421,7 +2426,7 @@
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="97" t="s">
+      <c r="J34" s="91" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="69" t="s">
@@ -2446,7 +2451,7 @@
       <c r="X34" s="36"/>
       <c r="Y34" s="36"/>
       <c r="Z34" s="36"/>
-      <c r="AA34" s="97" t="s">
+      <c r="AA34" s="91" t="s">
         <v>24</v>
       </c>
       <c r="AB34" s="36"/>
@@ -2457,9 +2462,9 @@
       <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
-      <c r="B35" s="94"/>
-      <c r="C35" s="97"/>
+      <c r="A35" s="96"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="91"/>
       <c r="D35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="97"/>
+      <c r="J35" s="91"/>
       <c r="K35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2495,7 +2500,7 @@
       <c r="X35" s="36"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
-      <c r="AA35" s="97"/>
+      <c r="AA35" s="91"/>
       <c r="AB35" s="36"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
@@ -2504,9 +2509,9 @@
       <c r="AG35" s="36"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="91"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="97"/>
+      <c r="A36" s="96"/>
+      <c r="B36" s="104"/>
+      <c r="C36" s="91"/>
       <c r="D36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2519,7 +2524,7 @@
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-      <c r="J36" s="97"/>
+      <c r="J36" s="91"/>
       <c r="K36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2542,7 +2547,7 @@
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="97"/>
+      <c r="AA36" s="91"/>
       <c r="AB36" s="36"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
@@ -2551,9 +2556,9 @@
       <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="91"/>
-      <c r="B37" s="94"/>
-      <c r="C37" s="97"/>
+      <c r="A37" s="96"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="47" t="s">
         <v>22</v>
       </c>
@@ -2566,7 +2571,7 @@
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="97"/>
+      <c r="J37" s="91"/>
       <c r="K37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2589,7 +2594,7 @@
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
-      <c r="AA37" s="97"/>
+      <c r="AA37" s="91"/>
       <c r="AB37" s="36"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
@@ -2598,11 +2603,11 @@
       <c r="AG37" s="36"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="91"/>
-      <c r="B38" s="95" t="s">
+      <c r="A38" s="96"/>
+      <c r="B38" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="97"/>
+      <c r="C38" s="91"/>
       <c r="D38" s="53"/>
       <c r="E38" s="60">
         <v>10793</v>
@@ -2613,7 +2618,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="97"/>
+      <c r="J38" s="91"/>
       <c r="K38" s="53"/>
       <c r="L38" s="63">
         <v>10794</v>
@@ -2634,7 +2639,7 @@
       <c r="X38" s="32"/>
       <c r="Y38" s="32"/>
       <c r="Z38" s="32"/>
-      <c r="AA38" s="97"/>
+      <c r="AA38" s="91"/>
       <c r="AB38" s="32"/>
       <c r="AC38" s="18"/>
       <c r="AD38" s="18"/>
@@ -2643,9 +2648,9 @@
       <c r="AG38" s="32"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="91"/>
-      <c r="B39" s="94"/>
-      <c r="C39" s="97"/>
+      <c r="A39" s="96"/>
+      <c r="B39" s="104"/>
+      <c r="C39" s="91"/>
       <c r="D39" s="53"/>
       <c r="E39" s="60">
         <v>10793</v>
@@ -2656,7 +2661,7 @@
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="97"/>
+      <c r="J39" s="91"/>
       <c r="K39" s="53"/>
       <c r="L39" s="63">
         <v>10794</v>
@@ -2677,7 +2682,7 @@
       <c r="X39" s="32"/>
       <c r="Y39" s="32"/>
       <c r="Z39" s="32"/>
-      <c r="AA39" s="97"/>
+      <c r="AA39" s="91"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="19"/>
       <c r="AD39" s="19"/>
@@ -2686,9 +2691,9 @@
       <c r="AG39" s="32"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="91"/>
-      <c r="B40" s="94"/>
-      <c r="C40" s="97"/>
+      <c r="A40" s="96"/>
+      <c r="B40" s="104"/>
+      <c r="C40" s="91"/>
       <c r="D40" s="56"/>
       <c r="E40" s="60">
         <v>10793</v>
@@ -2699,7 +2704,7 @@
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
-      <c r="J40" s="97"/>
+      <c r="J40" s="91"/>
       <c r="K40" s="54"/>
       <c r="L40" s="66">
         <v>10794</v>
@@ -2720,7 +2725,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="54"/>
       <c r="Z40" s="54"/>
-      <c r="AA40" s="97"/>
+      <c r="AA40" s="91"/>
       <c r="AB40" s="54"/>
       <c r="AC40" s="33"/>
       <c r="AD40" s="33"/>
@@ -2729,13 +2734,13 @@
       <c r="AG40" s="54"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="90">
+      <c r="A41" s="95">
         <v>46023</v>
       </c>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="104" t="s">
+      <c r="C41" s="101" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37"/>
@@ -2792,9 +2797,9 @@
       <c r="AG41" s="20"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="91"/>
-      <c r="B42" s="94"/>
-      <c r="C42" s="97"/>
+      <c r="A42" s="96"/>
+      <c r="B42" s="104"/>
+      <c r="C42" s="91"/>
       <c r="D42" s="36"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -2849,9 +2854,9 @@
       <c r="AG42" s="17"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="91"/>
-      <c r="B43" s="94"/>
-      <c r="C43" s="97"/>
+      <c r="A43" s="96"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="91"/>
       <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -2906,9 +2911,9 @@
       <c r="AG43" s="17"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="91"/>
-      <c r="B44" s="94"/>
-      <c r="C44" s="97"/>
+      <c r="A44" s="96"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="91"/>
       <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -2963,11 +2968,11 @@
       <c r="AG44" s="17"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="91"/>
-      <c r="B45" s="95" t="s">
+      <c r="A45" s="96"/>
+      <c r="B45" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="97"/>
+      <c r="C45" s="91"/>
       <c r="D45" s="32"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -3020,9 +3025,9 @@
       <c r="AG45" s="18"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="91"/>
-      <c r="B46" s="94"/>
-      <c r="C46" s="97"/>
+      <c r="A46" s="96"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="91"/>
       <c r="D46" s="32"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
@@ -3075,9 +3080,9 @@
       <c r="AG46" s="19"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="92"/>
-      <c r="B47" s="96"/>
-      <c r="C47" s="105"/>
+      <c r="A47" s="97"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="102"/>
       <c r="D47" s="34"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
@@ -3128,10 +3133,10 @@
       <c r="AG47" s="21"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="90">
+      <c r="A48" s="95">
         <v>46054</v>
       </c>
-      <c r="B48" s="93" t="s">
+      <c r="B48" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="39"/>
@@ -3160,7 +3165,7 @@
       <c r="P48" s="39"/>
       <c r="Q48" s="39"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="98" t="s">
+      <c r="S48" s="92" t="s">
         <v>26</v>
       </c>
       <c r="T48" s="82">
@@ -3187,8 +3192,8 @@
       <c r="AG48" s="43"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="91"/>
-      <c r="B49" s="94"/>
+      <c r="A49" s="96"/>
+      <c r="B49" s="104"/>
       <c r="C49" s="40"/>
       <c r="D49" s="36"/>
       <c r="E49" s="68" t="s">
@@ -3215,7 +3220,7 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="36"/>
-      <c r="S49" s="99"/>
+      <c r="S49" s="93"/>
       <c r="T49" s="67">
         <v>5425</v>
       </c>
@@ -3240,8 +3245,8 @@
       <c r="AG49" s="44"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="91"/>
-      <c r="B50" s="94"/>
+      <c r="A50" s="96"/>
+      <c r="B50" s="104"/>
       <c r="C50" s="40"/>
       <c r="D50" s="36"/>
       <c r="E50" s="68" t="s">
@@ -3268,7 +3273,7 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="36"/>
-      <c r="S50" s="99"/>
+      <c r="S50" s="93"/>
       <c r="T50" s="67">
         <v>5425</v>
       </c>
@@ -3293,8 +3298,8 @@
       <c r="AG50" s="44"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="91"/>
-      <c r="B51" s="94"/>
+      <c r="A51" s="96"/>
+      <c r="B51" s="104"/>
       <c r="C51" s="40"/>
       <c r="D51" s="36"/>
       <c r="E51" s="68" t="s">
@@ -3321,7 +3326,7 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="36"/>
-      <c r="S51" s="99"/>
+      <c r="S51" s="93"/>
       <c r="T51" s="67">
         <v>5425</v>
       </c>
@@ -3346,8 +3351,8 @@
       <c r="AG51" s="44"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="91"/>
-      <c r="B52" s="95" t="s">
+      <c r="A52" s="96"/>
+      <c r="B52" s="103" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="41"/>
@@ -3376,7 +3381,7 @@
       <c r="P52" s="41"/>
       <c r="Q52" s="41"/>
       <c r="R52" s="32"/>
-      <c r="S52" s="99"/>
+      <c r="S52" s="93"/>
       <c r="T52" s="67">
         <v>5425</v>
       </c>
@@ -3401,8 +3406,8 @@
       <c r="AG52" s="45"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="91"/>
-      <c r="B53" s="94"/>
+      <c r="A53" s="96"/>
+      <c r="B53" s="104"/>
       <c r="C53" s="41"/>
       <c r="D53" s="32"/>
       <c r="E53" s="63">
@@ -3429,7 +3434,7 @@
       <c r="P53" s="41"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="32"/>
-      <c r="S53" s="99"/>
+      <c r="S53" s="93"/>
       <c r="T53" s="67">
         <v>5425</v>
       </c>
@@ -3454,8 +3459,8 @@
       <c r="AG53" s="45"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
-      <c r="B54" s="96"/>
+      <c r="A54" s="97"/>
+      <c r="B54" s="106"/>
       <c r="C54" s="42"/>
       <c r="D54" s="34"/>
       <c r="E54" s="64">
@@ -3482,7 +3487,7 @@
       <c r="P54" s="42"/>
       <c r="Q54" s="42"/>
       <c r="R54" s="34"/>
-      <c r="S54" s="100"/>
+      <c r="S54" s="94"/>
       <c r="T54" s="34"/>
       <c r="U54" s="83">
         <v>5425</v>
@@ -3506,6 +3511,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3522,11 +3532,6 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/horario_status.xlsx
+++ b/horario_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Slyther1n\Desktop\iefp_formacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521FBBE4-46C8-476E-B5EA-466C4F5327EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A3A5B8-FE7B-4F64-B5A7-66E59E1F3980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4FA6E67-634F-4E5A-B3C1-BB1AE50EBAF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="29">
   <si>
     <t>Código</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>TrabalhoFad</t>
-  </si>
-  <si>
-    <t>MinorFixNoSpaceInv</t>
   </si>
 </sst>
 </file>
@@ -889,6 +886,27 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -901,15 +919,6 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="7" fillId="17" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -924,18 +933,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1435,9 +1432,7 @@
       <c r="E14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F14" s="14"/>
     </row>
     <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
@@ -1537,17 +1532,17 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="95">
+      <c r="A20" s="91">
         <v>45931</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="94" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
       <c r="E20" s="26"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="98" t="s">
+      <c r="G20" s="102" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="28"/>
@@ -1606,13 +1601,13 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="96"/>
-      <c r="B21" s="104"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="95"/>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="22"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="99"/>
+      <c r="G21" s="103"/>
       <c r="H21" s="29"/>
       <c r="I21" s="51"/>
       <c r="J21" s="57">
@@ -1669,13 +1664,13 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="96"/>
-      <c r="B22" s="104"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="95"/>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="22"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="99"/>
+      <c r="G22" s="103"/>
       <c r="H22" s="29"/>
       <c r="I22" s="51"/>
       <c r="J22" s="57">
@@ -1732,13 +1727,13 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="96"/>
-      <c r="B23" s="104"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="95"/>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="22"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="99"/>
+      <c r="G23" s="103"/>
       <c r="H23" s="29"/>
       <c r="I23" s="51"/>
       <c r="J23" s="52"/>
@@ -1793,15 +1788,15 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="96"/>
-      <c r="B24" s="103" t="s">
+      <c r="A24" s="92"/>
+      <c r="B24" s="96" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="99"/>
+      <c r="G24" s="103"/>
       <c r="H24" s="32"/>
       <c r="I24" s="51"/>
       <c r="J24" s="57">
@@ -1856,13 +1851,13 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="96"/>
-      <c r="B25" s="104"/>
+      <c r="A25" s="92"/>
+      <c r="B25" s="95"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="99"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="32"/>
       <c r="I25" s="51"/>
       <c r="J25" s="57">
@@ -1917,13 +1912,13 @@
       </c>
     </row>
     <row r="26" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="97"/>
-      <c r="B26" s="106"/>
+      <c r="A26" s="93"/>
+      <c r="B26" s="97"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
       <c r="E26" s="55"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="100"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="34"/>
       <c r="I26" s="55"/>
       <c r="J26" s="58">
@@ -1978,10 +1973,10 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="95">
+      <c r="A27" s="91">
         <v>45962</v>
       </c>
-      <c r="B27" s="105" t="s">
+      <c r="B27" s="94" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="20"/>
@@ -2049,8 +2044,8 @@
       <c r="AG27" s="27"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="96"/>
-      <c r="B28" s="104"/>
+      <c r="A28" s="92"/>
+      <c r="B28" s="95"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="49" t="s">
@@ -2116,8 +2111,8 @@
       <c r="AG28" s="25"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="96"/>
-      <c r="B29" s="104"/>
+      <c r="A29" s="92"/>
+      <c r="B29" s="95"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="49" t="s">
@@ -2183,8 +2178,8 @@
       <c r="AG29" s="25"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="96"/>
-      <c r="B30" s="104"/>
+      <c r="A30" s="92"/>
+      <c r="B30" s="95"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="49" t="s">
@@ -2250,8 +2245,8 @@
       <c r="AG30" s="25"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="96"/>
-      <c r="B31" s="103" t="s">
+      <c r="A31" s="92"/>
+      <c r="B31" s="96" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="18"/>
@@ -2303,8 +2298,8 @@
       <c r="AG31" s="25"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="96"/>
-      <c r="B32" s="104"/>
+      <c r="A32" s="92"/>
+      <c r="B32" s="95"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="51"/>
@@ -2354,8 +2349,8 @@
       <c r="AG32" s="25"/>
     </row>
     <row r="33" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="97"/>
-      <c r="B33" s="106"/>
+      <c r="A33" s="93"/>
+      <c r="B33" s="97"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
       <c r="E33" s="55"/>
@@ -2405,13 +2400,13 @@
       <c r="AG33" s="35"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="96">
+      <c r="A34" s="92">
         <v>45992</v>
       </c>
-      <c r="B34" s="104" t="s">
+      <c r="B34" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="98" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="69" t="s">
@@ -2426,7 +2421,7 @@
       </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="91" t="s">
+      <c r="J34" s="98" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="69" t="s">
@@ -2451,7 +2446,7 @@
       <c r="X34" s="36"/>
       <c r="Y34" s="36"/>
       <c r="Z34" s="36"/>
-      <c r="AA34" s="91" t="s">
+      <c r="AA34" s="98" t="s">
         <v>24</v>
       </c>
       <c r="AB34" s="36"/>
@@ -2462,9 +2457,9 @@
       <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="96"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="91"/>
+      <c r="A35" s="92"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="98"/>
       <c r="D35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2477,7 +2472,7 @@
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="91"/>
+      <c r="J35" s="98"/>
       <c r="K35" s="47" t="s">
         <v>22</v>
       </c>
@@ -2500,7 +2495,7 @@
       <c r="X35" s="36"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
-      <c r="AA35" s="91"/>
+      <c r="AA35" s="98"/>
       <c r="AB35" s="36"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="17"/>
@@ -2509,9 +2504,9 @@
       <c r="AG35" s="36"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="96"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="91"/>
+      <c r="A36" s="92"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="98"/>
       <c r="D36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2524,7 +2519,7 @@
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
-      <c r="J36" s="91"/>
+      <c r="J36" s="98"/>
       <c r="K36" s="47" t="s">
         <v>22</v>
       </c>
@@ -2547,7 +2542,7 @@
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
-      <c r="AA36" s="91"/>
+      <c r="AA36" s="98"/>
       <c r="AB36" s="36"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="17"/>
@@ -2556,9 +2551,9 @@
       <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="96"/>
-      <c r="B37" s="104"/>
-      <c r="C37" s="91"/>
+      <c r="A37" s="92"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="98"/>
       <c r="D37" s="47" t="s">
         <v>22</v>
       </c>
@@ -2571,7 +2566,7 @@
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="91"/>
+      <c r="J37" s="98"/>
       <c r="K37" s="48" t="s">
         <v>23</v>
       </c>
@@ -2594,7 +2589,7 @@
       <c r="X37" s="36"/>
       <c r="Y37" s="36"/>
       <c r="Z37" s="36"/>
-      <c r="AA37" s="91"/>
+      <c r="AA37" s="98"/>
       <c r="AB37" s="36"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
@@ -2603,11 +2598,11 @@
       <c r="AG37" s="36"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="96"/>
-      <c r="B38" s="103" t="s">
+      <c r="A38" s="92"/>
+      <c r="B38" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="91"/>
+      <c r="C38" s="98"/>
       <c r="D38" s="53"/>
       <c r="E38" s="60">
         <v>10793</v>
@@ -2618,7 +2613,7 @@
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
-      <c r="J38" s="91"/>
+      <c r="J38" s="98"/>
       <c r="K38" s="53"/>
       <c r="L38" s="63">
         <v>10794</v>
@@ -2639,7 +2634,7 @@
       <c r="X38" s="32"/>
       <c r="Y38" s="32"/>
       <c r="Z38" s="32"/>
-      <c r="AA38" s="91"/>
+      <c r="AA38" s="98"/>
       <c r="AB38" s="32"/>
       <c r="AC38" s="18"/>
       <c r="AD38" s="18"/>
@@ -2648,9 +2643,9 @@
       <c r="AG38" s="32"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="96"/>
-      <c r="B39" s="104"/>
-      <c r="C39" s="91"/>
+      <c r="A39" s="92"/>
+      <c r="B39" s="95"/>
+      <c r="C39" s="98"/>
       <c r="D39" s="53"/>
       <c r="E39" s="60">
         <v>10793</v>
@@ -2661,7 +2656,7 @@
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="91"/>
+      <c r="J39" s="98"/>
       <c r="K39" s="53"/>
       <c r="L39" s="63">
         <v>10794</v>
@@ -2682,7 +2677,7 @@
       <c r="X39" s="32"/>
       <c r="Y39" s="32"/>
       <c r="Z39" s="32"/>
-      <c r="AA39" s="91"/>
+      <c r="AA39" s="98"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="19"/>
       <c r="AD39" s="19"/>
@@ -2691,9 +2686,9 @@
       <c r="AG39" s="32"/>
     </row>
     <row r="40" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96"/>
-      <c r="B40" s="104"/>
-      <c r="C40" s="91"/>
+      <c r="A40" s="92"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="98"/>
       <c r="D40" s="56"/>
       <c r="E40" s="60">
         <v>10793</v>
@@ -2704,7 +2699,7 @@
       </c>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
-      <c r="J40" s="91"/>
+      <c r="J40" s="98"/>
       <c r="K40" s="54"/>
       <c r="L40" s="66">
         <v>10794</v>
@@ -2725,7 +2720,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="54"/>
       <c r="Z40" s="54"/>
-      <c r="AA40" s="91"/>
+      <c r="AA40" s="98"/>
       <c r="AB40" s="54"/>
       <c r="AC40" s="33"/>
       <c r="AD40" s="33"/>
@@ -2734,13 +2729,13 @@
       <c r="AG40" s="54"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="95">
+      <c r="A41" s="91">
         <v>46023</v>
       </c>
-      <c r="B41" s="105" t="s">
+      <c r="B41" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="101" t="s">
+      <c r="C41" s="105" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="37"/>
@@ -2797,9 +2792,9 @@
       <c r="AG41" s="20"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="96"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="91"/>
+      <c r="A42" s="92"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="98"/>
       <c r="D42" s="36"/>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -2854,9 +2849,9 @@
       <c r="AG42" s="17"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="96"/>
-      <c r="B43" s="104"/>
-      <c r="C43" s="91"/>
+      <c r="A43" s="92"/>
+      <c r="B43" s="95"/>
+      <c r="C43" s="98"/>
       <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -2911,9 +2906,9 @@
       <c r="AG43" s="17"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="96"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="91"/>
+      <c r="A44" s="92"/>
+      <c r="B44" s="95"/>
+      <c r="C44" s="98"/>
       <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -2968,11 +2963,11 @@
       <c r="AG44" s="17"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="96"/>
-      <c r="B45" s="103" t="s">
+      <c r="A45" s="92"/>
+      <c r="B45" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="91"/>
+      <c r="C45" s="98"/>
       <c r="D45" s="32"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
@@ -3025,9 +3020,9 @@
       <c r="AG45" s="18"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="96"/>
-      <c r="B46" s="104"/>
-      <c r="C46" s="91"/>
+      <c r="A46" s="92"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="98"/>
       <c r="D46" s="32"/>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
@@ -3080,9 +3075,9 @@
       <c r="AG46" s="19"/>
     </row>
     <row r="47" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="97"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="102"/>
+      <c r="A47" s="93"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="106"/>
       <c r="D47" s="34"/>
       <c r="E47" s="21"/>
       <c r="F47" s="21"/>
@@ -3133,10 +3128,10 @@
       <c r="AG47" s="21"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="95">
+      <c r="A48" s="91">
         <v>46054</v>
       </c>
-      <c r="B48" s="105" t="s">
+      <c r="B48" s="94" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="39"/>
@@ -3165,7 +3160,7 @@
       <c r="P48" s="39"/>
       <c r="Q48" s="39"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="92" t="s">
+      <c r="S48" s="99" t="s">
         <v>26</v>
       </c>
       <c r="T48" s="82">
@@ -3192,8 +3187,8 @@
       <c r="AG48" s="43"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="96"/>
-      <c r="B49" s="104"/>
+      <c r="A49" s="92"/>
+      <c r="B49" s="95"/>
       <c r="C49" s="40"/>
       <c r="D49" s="36"/>
       <c r="E49" s="68" t="s">
@@ -3220,7 +3215,7 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="36"/>
-      <c r="S49" s="93"/>
+      <c r="S49" s="100"/>
       <c r="T49" s="67">
         <v>5425</v>
       </c>
@@ -3245,8 +3240,8 @@
       <c r="AG49" s="44"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="96"/>
-      <c r="B50" s="104"/>
+      <c r="A50" s="92"/>
+      <c r="B50" s="95"/>
       <c r="C50" s="40"/>
       <c r="D50" s="36"/>
       <c r="E50" s="68" t="s">
@@ -3273,7 +3268,7 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="36"/>
-      <c r="S50" s="93"/>
+      <c r="S50" s="100"/>
       <c r="T50" s="67">
         <v>5425</v>
       </c>
@@ -3298,8 +3293,8 @@
       <c r="AG50" s="44"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="96"/>
-      <c r="B51" s="104"/>
+      <c r="A51" s="92"/>
+      <c r="B51" s="95"/>
       <c r="C51" s="40"/>
       <c r="D51" s="36"/>
       <c r="E51" s="68" t="s">
@@ -3326,7 +3321,7 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="36"/>
-      <c r="S51" s="93"/>
+      <c r="S51" s="100"/>
       <c r="T51" s="67">
         <v>5425</v>
       </c>
@@ -3351,8 +3346,8 @@
       <c r="AG51" s="44"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="96"/>
-      <c r="B52" s="103" t="s">
+      <c r="A52" s="92"/>
+      <c r="B52" s="96" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="41"/>
@@ -3381,7 +3376,7 @@
       <c r="P52" s="41"/>
       <c r="Q52" s="41"/>
       <c r="R52" s="32"/>
-      <c r="S52" s="93"/>
+      <c r="S52" s="100"/>
       <c r="T52" s="67">
         <v>5425</v>
       </c>
@@ -3406,8 +3401,8 @@
       <c r="AG52" s="45"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="96"/>
-      <c r="B53" s="104"/>
+      <c r="A53" s="92"/>
+      <c r="B53" s="95"/>
       <c r="C53" s="41"/>
       <c r="D53" s="32"/>
       <c r="E53" s="63">
@@ -3434,7 +3429,7 @@
       <c r="P53" s="41"/>
       <c r="Q53" s="41"/>
       <c r="R53" s="32"/>
-      <c r="S53" s="93"/>
+      <c r="S53" s="100"/>
       <c r="T53" s="67">
         <v>5425</v>
       </c>
@@ -3459,8 +3454,8 @@
       <c r="AG53" s="45"/>
     </row>
     <row r="54" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="97"/>
-      <c r="B54" s="106"/>
+      <c r="A54" s="93"/>
+      <c r="B54" s="97"/>
       <c r="C54" s="42"/>
       <c r="D54" s="34"/>
       <c r="E54" s="64">
@@ -3487,7 +3482,7 @@
       <c r="P54" s="42"/>
       <c r="Q54" s="42"/>
       <c r="R54" s="34"/>
-      <c r="S54" s="94"/>
+      <c r="S54" s="101"/>
       <c r="T54" s="34"/>
       <c r="U54" s="83">
         <v>5425</v>
@@ -3511,11 +3506,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="J34:J40"/>
     <mergeCell ref="AA34:AA40"/>
     <mergeCell ref="C34:C40"/>
     <mergeCell ref="S48:S54"/>
@@ -3532,6 +3522,11 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B54"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="J34:J40"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
